--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="83">
   <si>
     <t>DRV</t>
   </si>
@@ -657,6 +657,12 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
@@ -668,6 +674,12 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
@@ -679,6 +691,12 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
@@ -707,6 +725,12 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
@@ -718,6 +742,12 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
@@ -729,6 +759,12 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
       <c r="C9" t="s">
         <v>30</v>
       </c>
@@ -757,6 +793,12 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
       <c r="C11" t="s">
         <v>38</v>
       </c>
@@ -768,6 +810,12 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
       <c r="C12" t="s">
         <v>41</v>
       </c>
@@ -779,6 +827,12 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
       <c r="C13" t="s">
         <v>44</v>
       </c>
@@ -807,6 +861,12 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
       <c r="C15" t="s">
         <v>51</v>
       </c>
@@ -818,6 +878,12 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
       <c r="C16" t="s">
         <v>54</v>
       </c>
@@ -829,6 +895,12 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
       <c r="C17" t="s">
         <v>57</v>
       </c>
@@ -857,6 +929,12 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
       <c r="C19" t="s">
         <v>63</v>
       </c>
@@ -868,6 +946,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
       <c r="C20" t="s">
         <v>65</v>
       </c>
@@ -879,6 +963,12 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
       <c r="C21" t="s">
         <v>68</v>
       </c>
@@ -907,6 +997,12 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
       <c r="C23" t="s">
         <v>76</v>
       </c>
@@ -918,6 +1014,12 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
       <c r="C24" t="s">
         <v>76</v>
       </c>
@@ -929,6 +1031,12 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
       <c r="C25" t="s">
         <v>81</v>
       </c>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="121">
   <si>
     <t>DRV</t>
   </si>
@@ -273,13 +273,127 @@
   </si>
   <si>
     <t>pvt_mwadk194</t>
+  </si>
+  <si>
+    <t>KABBU</t>
+  </si>
+  <si>
+    <t>LOGIN_VENDEUR</t>
+  </si>
+  <si>
+    <t>SUD</t>
+  </si>
+  <si>
+    <t>PVT MOR WADE KOLDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVT SEYDINA OUSMANE SY </t>
+  </si>
+  <si>
+    <t>Abdoulaye</t>
+  </si>
+  <si>
+    <t> 771883753</t>
+  </si>
+  <si>
+    <t> 775801980</t>
+  </si>
+  <si>
+    <t>ADAMA</t>
+  </si>
+  <si>
+    <t>pvt_sosy150</t>
+  </si>
+  <si>
+    <t> 771883900</t>
+  </si>
+  <si>
+    <t> 781596632</t>
+  </si>
+  <si>
+    <t>EST</t>
+  </si>
+  <si>
+    <t>PVT DEMBA FALL DE FATICK</t>
+  </si>
+  <si>
+    <t> 787567059</t>
+  </si>
+  <si>
+    <t>Dabo</t>
+  </si>
+  <si>
+    <t> 787655204</t>
+  </si>
+  <si>
+    <t>NORD</t>
+  </si>
+  <si>
+    <t>PVT MADINA BUSINESS PRO LINGUERE</t>
+  </si>
+  <si>
+    <t> 776003741</t>
+  </si>
+  <si>
+    <t>MASSOUDA DIENG</t>
+  </si>
+  <si>
+    <t>FALL</t>
+  </si>
+  <si>
+    <t>Pvt_mbpling0224</t>
+  </si>
+  <si>
+    <t> 787095631</t>
+  </si>
+  <si>
+    <t> 787095625</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DEMBA SOUMARE </t>
+  </si>
+  <si>
+    <t> DIOUF</t>
+  </si>
+  <si>
+    <t> Pvt_mbpling173</t>
+  </si>
+  <si>
+    <t> 776006374</t>
+  </si>
+  <si>
+    <t>CENTRE</t>
+  </si>
+  <si>
+    <t>SERIGNE MBACKE MADINA CISSE</t>
+  </si>
+  <si>
+    <t>TEKNICOM CONSULTING GROUPE</t>
+  </si>
+  <si>
+    <t>OUSMANE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDIAYE </t>
+  </si>
+  <si>
+    <t>pvt_tcg_0078</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>MODOU</t>
+  </si>
+  <si>
+    <t>pvt_smmc2928</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,16 +406,53 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1A983"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -324,15 +475,336 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -613,8 +1085,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
@@ -622,7 +1094,7 @@
     <col min="5" max="5" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="28" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,8 +1110,27 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="26">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -655,8 +1146,29 @@
       <c r="E2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2">
+        <v>782989910</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="9">
+        <v>775810336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="38.5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -672,8 +1184,25 @@
       <c r="E3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <v>787095594</v>
+      </c>
+      <c r="J3" s="10"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="O3" s="13">
+        <v>772107591</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="26">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -689,8 +1218,25 @@
       <c r="E4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4">
+        <v>781180981</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="O4" s="13">
+        <v>772104981</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="26.5" thickBot="1">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -706,8 +1252,25 @@
       <c r="E5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <v>787095584</v>
+      </c>
+      <c r="J5" s="14"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="O5" s="17">
+        <v>778525987</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -723,8 +1286,29 @@
       <c r="E6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6">
+        <v>786241266</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="26">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -732,16 +1316,33 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+      <c r="F7">
+        <v>789160174</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="O7" s="19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -757,8 +1358,25 @@
       <c r="E8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8">
+        <v>786241255</v>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="O8" s="19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="26.5" thickBot="1">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -774,8 +1392,25 @@
       <c r="E9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9">
+        <v>775812208</v>
+      </c>
+      <c r="J9" s="14"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="26">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -791,8 +1426,29 @@
       <c r="E10" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="26">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -808,8 +1464,25 @@
       <c r="E11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" s="10"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" s="21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="26">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -825,8 +1498,25 @@
       <c r="E12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <v>778528509</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" s="13">
+        <v>778528509</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="26.5" thickBot="1">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -842,8 +1532,25 @@
       <c r="E13" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F13">
+        <v>787655222</v>
+      </c>
+      <c r="J13" s="14"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13" s="17">
+        <v>787655222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="26">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -859,8 +1566,29 @@
       <c r="E14" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F14" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="O14" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="26">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -876,8 +1604,23 @@
       <c r="E15" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F15" s="26"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="26">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -893,8 +1636,25 @@
       <c r="E16" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F16" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16" s="10"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="25.5" thickBot="1">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -910,8 +1670,25 @@
       <c r="E17" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" s="14"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="O17" s="24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="26.5" thickBot="1">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -927,8 +1704,29 @@
       <c r="E18" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="25">
+        <v>786241255</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="26.5" thickBot="1">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -944,8 +1742,25 @@
       <c r="E19" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19" t="s">
+        <v>90</v>
+      </c>
+      <c r="J19" s="10"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="25">
+        <v>775812208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="26.5" thickBot="1">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -961,8 +1776,25 @@
       <c r="E20" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20" t="s">
+        <v>94</v>
+      </c>
+      <c r="J20" s="10"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" s="25">
+        <v>786241266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="26.5" thickBot="1">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -978,8 +1810,23 @@
       <c r="E21" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21" s="26"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" s="25">
+        <v>786239376</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="26">
       <c r="A22" t="s">
         <v>71</v>
       </c>
@@ -995,8 +1842,29 @@
       <c r="E22" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22">
+        <v>775810336</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="O22" s="18">
+        <v>787095594</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="26">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -1012,8 +1880,25 @@
       <c r="E23" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23">
+        <v>778525987</v>
+      </c>
+      <c r="J23" s="10"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23" s="19">
+        <v>787095584</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="26">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -1029,8 +1914,25 @@
       <c r="E24" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24">
+        <v>772104981</v>
+      </c>
+      <c r="J24" s="10"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="O24" s="19">
+        <v>782989910</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="26.5" thickBot="1">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1046,8 +1948,39 @@
       <c r="E25" t="s">
         <v>82</v>
       </c>
+      <c r="F25">
+        <v>772107591</v>
+      </c>
+      <c r="J25" s="14"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="O25" s="20">
+        <v>777411462</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="J14:J17"/>
+    <mergeCell ref="K14:K17"/>
+    <mergeCell ref="J18:J21"/>
+    <mergeCell ref="K18:K21"/>
+    <mergeCell ref="J22:J25"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="J2:J5"/>
+    <mergeCell ref="K2:K5"/>
+    <mergeCell ref="J6:J9"/>
+    <mergeCell ref="K6:K9"/>
+    <mergeCell ref="J10:J13"/>
+    <mergeCell ref="K10:K13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="152">
   <si>
     <t>DRV</t>
   </si>
@@ -300,13 +301,193 @@
   </si>
   <si>
     <t>pvt_smmc2928</t>
+  </si>
+  <si>
+    <t>PVT ITR KAFFRINE</t>
+  </si>
+  <si>
+    <t>SEYNABOU</t>
+  </si>
+  <si>
+    <t>GAYE</t>
+  </si>
+  <si>
+    <t>pvt_itrkaf255</t>
+  </si>
+  <si>
+    <t>PAPE ABDOULAYE</t>
+  </si>
+  <si>
+    <t>pvt_itrkaf0585</t>
+  </si>
+  <si>
+    <t>ROKY</t>
+  </si>
+  <si>
+    <t>KEBE</t>
+  </si>
+  <si>
+    <t>pvt_itrkaf292</t>
+  </si>
+  <si>
+    <t>OUSMANE</t>
+  </si>
+  <si>
+    <t>THIALL</t>
+  </si>
+  <si>
+    <t>pvt_itrkaf192</t>
+  </si>
+  <si>
+    <t>NORD</t>
+  </si>
+  <si>
+    <t>PVT THOMAS DJIBRIL CISS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABDOU LAHAD </t>
+  </si>
+  <si>
+    <t>Pvt_tdc590013</t>
+  </si>
+  <si>
+    <t>ALLA  SOW</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABIBOU  </t>
+  </si>
+  <si>
+    <t>Pvt_tdc590120</t>
+  </si>
+  <si>
+    <t>BILALY</t>
+  </si>
+  <si>
+    <t>BASSOUM</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590016</t>
+  </si>
+  <si>
+    <t>PVT SORIKE FOFANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIEUX </t>
+  </si>
+  <si>
+    <t>DANSOKHO</t>
+  </si>
+  <si>
+    <t>pvt_sfof126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARIDIATOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DIALLO</t>
+  </si>
+  <si>
+    <t>pvt_sfof097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MADIALANG </t>
+  </si>
+  <si>
+    <t>DRAME</t>
+  </si>
+  <si>
+    <t>pvt_sfof0211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMADOU THIERNO </t>
+  </si>
+  <si>
+    <t>pvt_sfof0228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUD </t>
+  </si>
+  <si>
+    <t>PVT GIEZIGTELECOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BINTOU  </t>
+  </si>
+  <si>
+    <t>pvt_zigtel _ravt _zigt068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEAN EMMANUEL CHRISTOPHOR </t>
+  </si>
+  <si>
+    <t>BADJI</t>
+  </si>
+  <si>
+    <t>pvt_zigtel0351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FATOU </t>
+  </si>
+  <si>
+    <t>pvt_zigtel0316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDEYE FATOU  </t>
+  </si>
+  <si>
+    <t>MANE</t>
+  </si>
+  <si>
+    <t>pvt_zigtel281</t>
+  </si>
+  <si>
+    <t>PVT FALLOU NDIAYE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnima </t>
+  </si>
+  <si>
+    <t>Diatta</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1367</t>
+  </si>
+  <si>
+    <t>Rose Mendy</t>
+  </si>
+  <si>
+    <t>Mendy</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pauline coumba </t>
+  </si>
+  <si>
+    <t>Faye</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fallou </t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1719</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,6 +499,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -334,7 +523,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -357,16 +546,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
@@ -974,7 +1230,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -994,7 +1250,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -1014,7 +1270,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -1034,7 +1290,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1054,7 +1310,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -1072,7 +1328,7 @@
       </c>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -1092,7 +1348,7 @@
         <v>775810336</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -1112,7 +1368,7 @@
         <v>778525987</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>68</v>
       </c>
@@ -1132,7 +1388,7 @@
         <v>772104981</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>68</v>
       </c>
@@ -1149,6 +1405,618 @@
         <v>79</v>
       </c>
       <c r="F25">
+        <v>772107591</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="4">
+        <v>773097086</v>
+      </c>
+      <c r="G26" s="3">
+        <v>777410048</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="9"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="6">
+        <v>775545556</v>
+      </c>
+      <c r="G27" s="5">
+        <v>787656877</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="9"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="6">
+        <v>773460373</v>
+      </c>
+      <c r="G28" s="5">
+        <v>776019823</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="10"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="6">
+        <v>770617096</v>
+      </c>
+      <c r="G29" s="5">
+        <v>782981141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="3">
+        <v>777147559</v>
+      </c>
+      <c r="G30" s="3">
+        <v>788255458</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="11"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="5">
+        <v>777951348</v>
+      </c>
+      <c r="G31" s="5">
+        <v>789166919</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="11"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="5">
+        <v>782190772</v>
+      </c>
+      <c r="G32" s="5">
+        <v>789151415</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="11"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="5">
+        <v>789111270</v>
+      </c>
+      <c r="G33" s="5">
+        <v>789166998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="3">
+        <v>778847933</v>
+      </c>
+      <c r="G34" s="3">
+        <v>781180310</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="11"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" s="5">
+        <v>782651638</v>
+      </c>
+      <c r="G35" s="5">
+        <v>781180552</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="11"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" s="5">
+        <v>774790213</v>
+      </c>
+      <c r="G36" s="5">
+        <v>787080588</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="11"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F37" s="5">
+        <v>788780692</v>
+      </c>
+      <c r="G37" s="5">
+        <v>789150406</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F38" s="3">
+        <v>777509848</v>
+      </c>
+      <c r="G38" s="3">
+        <v>771545210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="11"/>
+      <c r="B39" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F39" s="5">
+        <v>776919692</v>
+      </c>
+      <c r="G39" s="5">
+        <v>773958904</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="11"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" s="5">
+        <v>783008307</v>
+      </c>
+      <c r="G40" s="5">
+        <v>776950987</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="11"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F41" s="7">
+        <v>780123961</v>
+      </c>
+      <c r="G41" s="5">
+        <v>781825193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F42" s="5">
+        <v>778679190</v>
+      </c>
+      <c r="G42" s="3">
+        <v>786180521</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F43" s="5">
+        <v>771994713</v>
+      </c>
+      <c r="G43" s="5">
+        <v>786183517</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F44" s="5">
+        <v>784119644</v>
+      </c>
+      <c r="G44" s="5">
+        <v>772118585</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="10"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F45" s="7">
+        <v>787389275</v>
+      </c>
+      <c r="G45" s="7">
+        <v>787389275</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>782989910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>787095594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>781180981</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>787095584</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>786241266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7">
+        <v>789160174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>786241255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9">
+        <v>775812208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12">
+        <v>778528509</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13">
+        <v>787655222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22">
+        <v>775810336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23">
+        <v>778525987</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24">
+        <v>772104981</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25">
         <v>772107591</v>
       </c>
     </row>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -417,9 +417,6 @@
     <t xml:space="preserve">BINTOU  </t>
   </si>
   <si>
-    <t>pvt_zigtel _ravt _zigt068</t>
-  </si>
-  <si>
     <t xml:space="preserve">JEAN EMMANUEL CHRISTOPHOR </t>
   </si>
   <si>
@@ -481,6 +478,9 @@
   </si>
   <si>
     <t>pvt_tbogo1719</t>
+  </si>
+  <si>
+    <t>pvt_zigtel_ravt_zig068</t>
   </si>
 </sst>
 </file>
@@ -1662,7 +1662,7 @@
         <v>25</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="F38" s="3">
         <v>777509848</v>
@@ -1677,13 +1677,13 @@
         <v>105</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="F39" s="5">
         <v>776919692</v>
@@ -1696,13 +1696,13 @@
       <c r="A40" s="11"/>
       <c r="B40" s="13"/>
       <c r="C40" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40" s="5">
         <v>783008307</v>
@@ -1715,13 +1715,13 @@
       <c r="A41" s="11"/>
       <c r="B41" s="14"/>
       <c r="C41" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="E41" s="7" t="s">
         <v>137</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>138</v>
       </c>
       <c r="F41" s="7">
         <v>780123961</v>
@@ -1735,16 +1735,16 @@
         <v>19</v>
       </c>
       <c r="B42" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="F42" s="5">
         <v>778679190</v>
@@ -1757,13 +1757,13 @@
       <c r="A43" s="9"/>
       <c r="B43" s="13"/>
       <c r="C43" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="F43" s="5">
         <v>771994713</v>
@@ -1776,13 +1776,13 @@
       <c r="A44" s="9"/>
       <c r="B44" s="13"/>
       <c r="C44" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="F44" s="5">
         <v>784119644</v>
@@ -1795,13 +1795,13 @@
       <c r="A45" s="10"/>
       <c r="B45" s="14"/>
       <c r="C45" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="E45" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="F45" s="7">
         <v>787389275</v>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -12,8 +12,9 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="7010"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
+    <sheet name="vto" sheetId="1" r:id="rId1"/>
+    <sheet name="pvt" sheetId="3" r:id="rId2"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="159">
   <si>
     <t>DRV</t>
   </si>
@@ -303,9 +304,6 @@
     <t>pvt_smmc2928</t>
   </si>
   <si>
-    <t>PVT ITR KAFFRINE</t>
-  </si>
-  <si>
     <t>SEYNABOU</t>
   </si>
   <si>
@@ -342,9 +340,6 @@
     <t>NORD</t>
   </si>
   <si>
-    <t>PVT THOMAS DJIBRIL CISS</t>
-  </si>
-  <si>
     <t xml:space="preserve">ABDOU LAHAD </t>
   </si>
   <si>
@@ -372,9 +367,6 @@
     <t>Pvt_tdc590016</t>
   </si>
   <si>
-    <t>PVT SORIKE FOFANA</t>
-  </si>
-  <si>
     <t xml:space="preserve">VIEUX </t>
   </si>
   <si>
@@ -411,9 +403,6 @@
     <t xml:space="preserve">SUD </t>
   </si>
   <si>
-    <t>PVT GIEZIGTELECOM</t>
-  </si>
-  <si>
     <t xml:space="preserve">BINTOU  </t>
   </si>
   <si>
@@ -441,9 +430,6 @@
     <t>pvt_zigtel281</t>
   </si>
   <si>
-    <t>PVT FALLOU NDIAYE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gnima </t>
   </si>
   <si>
@@ -481,6 +467,42 @@
   </si>
   <si>
     <t>pvt_zigtel_ravt_zig068</t>
+  </si>
+  <si>
+    <t>CONTACT</t>
+  </si>
+  <si>
+    <t>DRC</t>
+  </si>
+  <si>
+    <t>DRE</t>
+  </si>
+  <si>
+    <t>PVT TOUBA BOGO COMMUNICATION (ZONE MBOUR)</t>
+  </si>
+  <si>
+    <t>PVT ITR (ZONE KAFFRINE)</t>
+  </si>
+  <si>
+    <t>DRN</t>
+  </si>
+  <si>
+    <t>PVT Thomas Djibril Ciss (RAVT KEBEMER)</t>
+  </si>
+  <si>
+    <t>DRSE</t>
+  </si>
+  <si>
+    <t>PVT FOFANA SORIKE KEDOUGOU (RAVT ZONE KEDOUGOU)</t>
+  </si>
+  <si>
+    <t>DRS</t>
+  </si>
+  <si>
+    <t>PVT ZIG TELECOM (RAVT ZIGUINCHOR)</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -587,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -608,20 +630,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -903,12 +926,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1412,17 +1435,17 @@
       <c r="A26" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="F26" s="4">
         <v>773097086</v>
@@ -1432,16 +1455,20 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="9"/>
-      <c r="B27" s="13"/>
+      <c r="A27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>151</v>
+      </c>
       <c r="C27" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F27" s="6">
         <v>775545556</v>
@@ -1451,16 +1478,20 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="9"/>
-      <c r="B28" s="13"/>
+      <c r="A28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>151</v>
+      </c>
       <c r="C28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="F28" s="6">
         <v>773460373</v>
@@ -1470,16 +1501,20 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="10"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>151</v>
+      </c>
       <c r="C29" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="F29" s="6">
         <v>770617096</v>
@@ -1489,20 +1524,20 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F30" s="3">
         <v>777147559</v>
@@ -1512,16 +1547,20 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="11"/>
-      <c r="B31" s="13"/>
+      <c r="A31" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>153</v>
+      </c>
       <c r="C31" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F31" s="5">
         <v>777951348</v>
@@ -1531,16 +1570,20 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="11"/>
-      <c r="B32" s="13"/>
+      <c r="A32" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>153</v>
+      </c>
       <c r="C32" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F32" s="5">
         <v>782190772</v>
@@ -1550,16 +1593,20 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="11"/>
-      <c r="B33" s="14"/>
+      <c r="A33" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>153</v>
+      </c>
       <c r="C33" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="F33" s="5">
         <v>789111270</v>
@@ -1569,20 +1616,20 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="F34" s="3">
         <v>778847933</v>
@@ -1592,16 +1639,20 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="11"/>
-      <c r="B35" s="13"/>
+      <c r="A35" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>155</v>
+      </c>
       <c r="C35" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F35" s="5">
         <v>782651638</v>
@@ -1611,16 +1662,20 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="11"/>
-      <c r="B36" s="13"/>
+      <c r="A36" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>155</v>
+      </c>
       <c r="C36" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F36" s="5">
         <v>774790213</v>
@@ -1630,16 +1685,20 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="11"/>
-      <c r="B37" s="14"/>
+      <c r="A37" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>155</v>
+      </c>
       <c r="C37" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>42</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F37" s="5">
         <v>788780692</v>
@@ -1649,20 +1708,20 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>128</v>
+      <c r="A38" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>157</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F38" s="3">
         <v>777509848</v>
@@ -1672,18 +1731,20 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="11"/>
+      <c r="A39" s="10" t="s">
+        <v>124</v>
+      </c>
       <c r="B39" s="13" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F39" s="5">
         <v>776919692</v>
@@ -1693,16 +1754,20 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="11"/>
-      <c r="B40" s="13"/>
+      <c r="A40" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>157</v>
+      </c>
       <c r="C40" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F40" s="5">
         <v>783008307</v>
@@ -1712,16 +1777,20 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="11"/>
-      <c r="B41" s="14"/>
+      <c r="A41" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>157</v>
+      </c>
       <c r="C41" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F41" s="7">
         <v>780123961</v>
@@ -1734,17 +1803,17 @@
       <c r="A42" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>138</v>
+      <c r="B42" s="13" t="s">
+        <v>150</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F42" s="5">
         <v>778679190</v>
@@ -1754,16 +1823,20 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="9"/>
-      <c r="B43" s="13"/>
+      <c r="A43" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>150</v>
+      </c>
       <c r="C43" s="5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F43" s="5">
         <v>771994713</v>
@@ -1773,16 +1846,20 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="9"/>
-      <c r="B44" s="13"/>
+      <c r="A44" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>150</v>
+      </c>
       <c r="C44" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F44" s="5">
         <v>784119644</v>
@@ -1792,16 +1869,20 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="10"/>
-      <c r="B45" s="14"/>
+      <c r="A45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>150</v>
+      </c>
       <c r="C45" s="7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F45" s="7">
         <v>787389275</v>
@@ -1810,12 +1891,259 @@
         <v>787389275</v>
       </c>
     </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C53" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C54" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C55" s="14"/>
+      <c r="D55" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C56" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C57" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C58" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C59" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C60" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C61" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C62" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C63" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C64" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="D64" s="13"/>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C62:C63"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="11">
+        <v>774981290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="11">
+        <v>775499999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="14"/>
+      <c r="B4" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="13"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="11">
+        <v>776247047</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="13">
+        <v>776665352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="11">
+        <v>775499999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="13">
+        <v>781287163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="13">
+        <v>772579898</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="11">
+        <v>774317541</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="11">
+        <v>773316647</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="13">
+        <v>775451818</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="158">
   <si>
     <t>DRV</t>
   </si>
@@ -500,9 +500,6 @@
   </si>
   <si>
     <t>PVT ZIG TELECOM (RAVT ZIGUINCHOR)</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -609,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -642,9 +639,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -926,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
@@ -1892,105 +1886,10 @@
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C53" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C54" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C55" s="14"/>
-      <c r="D55" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C56" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C57" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C58" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C59" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C60" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C61" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C62" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C63" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C64" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="D64" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C62:C63"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -445,9 +445,6 @@
     <t>Mendy</t>
   </si>
   <si>
-    <t>pvt_tbogo1368</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pauline coumba </t>
   </si>
   <si>
@@ -500,6 +497,9 @@
   </si>
   <si>
     <t>PVT ZIG TELECOM (RAVT ZIGUINCHOR)</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1124</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1430,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>92</v>
@@ -1453,7 +1453,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>95</v>
@@ -1476,7 +1476,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>97</v>
@@ -1499,7 +1499,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>100</v>
@@ -1522,7 +1522,7 @@
         <v>103</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>104</v>
@@ -1545,7 +1545,7 @@
         <v>103</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>106</v>
@@ -1568,7 +1568,7 @@
         <v>103</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>108</v>
@@ -1591,7 +1591,7 @@
         <v>103</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>110</v>
@@ -1614,7 +1614,7 @@
         <v>57</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>113</v>
@@ -1637,7 +1637,7 @@
         <v>57</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>116</v>
@@ -1660,7 +1660,7 @@
         <v>57</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>119</v>
@@ -1683,7 +1683,7 @@
         <v>57</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>122</v>
@@ -1706,7 +1706,7 @@
         <v>124</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>125</v>
@@ -1715,7 +1715,7 @@
         <v>25</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F38" s="3">
         <v>777509848</v>
@@ -1729,7 +1729,7 @@
         <v>124</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>126</v>
@@ -1752,7 +1752,7 @@
         <v>124</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>129</v>
@@ -1775,7 +1775,7 @@
         <v>124</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>131</v>
@@ -1798,7 +1798,7 @@
         <v>19</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>134</v>
@@ -1821,7 +1821,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>137</v>
@@ -1830,7 +1830,7 @@
         <v>138</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="F43" s="5">
         <v>771994713</v>
@@ -1844,16 +1844,16 @@
         <v>19</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C44" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="F44" s="5">
         <v>784119644</v>
@@ -1867,16 +1867,16 @@
         <v>19</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C45" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="E45" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="F45" s="7">
         <v>787389275</v>
@@ -1910,7 +1910,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1926,7 +1926,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>20</v>
@@ -1938,13 +1938,13 @@
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
       <c r="B4" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C4" s="13"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>31</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C6" s="13">
         <v>776665352</v>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>45</v>
@@ -1977,10 +1977,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>152</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>153</v>
       </c>
       <c r="C8" s="13">
         <v>781287163</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>154</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>155</v>
       </c>
       <c r="C9" s="13">
         <v>772579898</v>
@@ -1999,7 +1999,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>58</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>69</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>156</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>157</v>
       </c>
       <c r="C12" s="13">
         <v>775451818</v>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="7010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="7010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="vto" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="158">
   <si>
     <t>DRV</t>
   </si>
@@ -606,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -639,6 +639,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1925,7 +1928,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>147</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1936,7 +1939,9 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="14"/>
+      <c r="A4" s="15" t="s">
+        <v>147</v>
+      </c>
       <c r="B4" s="13" t="s">
         <v>149</v>
       </c>
@@ -2031,8 +2036,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A3:A4"/>
+  <mergeCells count="4">
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A9:A10"/>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="7010" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="7010"/>
   </bookViews>
   <sheets>
     <sheet name="vto" sheetId="1" r:id="rId1"/>
@@ -606,20 +606,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -638,10 +632,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1429,10 +1423,10 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>150</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -1444,87 +1438,87 @@
       <c r="E26" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F26" s="4">
-        <v>773097086</v>
+      <c r="F26" s="3">
+        <v>777410048</v>
       </c>
       <c r="G26" s="3">
         <v>777410048</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F27" s="6">
-        <v>775545556</v>
-      </c>
-      <c r="G27" s="5">
+      <c r="F27" s="4">
         <v>787656877</v>
       </c>
+      <c r="G27" s="4">
+        <v>787656877</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F28" s="6">
-        <v>773460373</v>
-      </c>
-      <c r="G28" s="5">
+      <c r="F28" s="4">
         <v>776019823</v>
       </c>
+      <c r="G28" s="4">
+        <v>776019823</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F29" s="6">
-        <v>770617096</v>
-      </c>
-      <c r="G29" s="5">
+      <c r="F29" s="4">
         <v>782981141</v>
       </c>
+      <c r="G29" s="4">
+        <v>782981141</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>152</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -1537,178 +1531,178 @@
         <v>105</v>
       </c>
       <c r="F30" s="3">
-        <v>777147559</v>
+        <v>788255458</v>
       </c>
       <c r="G30" s="3">
         <v>788255458</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F31" s="5">
-        <v>777951348</v>
-      </c>
-      <c r="G31" s="5">
+      <c r="F31" s="4">
         <v>789166919</v>
       </c>
+      <c r="G31" s="4">
+        <v>789166919</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F32" s="5">
-        <v>782190772</v>
-      </c>
-      <c r="G32" s="5">
+      <c r="F32" s="4">
         <v>789151415</v>
       </c>
+      <c r="G32" s="4">
+        <v>789151415</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="5">
-        <v>789111270</v>
-      </c>
-      <c r="G33" s="5">
+      <c r="F33" s="4">
         <v>789166998</v>
       </c>
+      <c r="G33" s="4">
+        <v>789166998</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="11" t="s">
         <v>154</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>114</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>115</v>
       </c>
       <c r="F34" s="3">
-        <v>778847933</v>
+        <v>781180310</v>
       </c>
       <c r="G34" s="3">
         <v>781180310</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F35" s="5">
-        <v>782651638</v>
-      </c>
-      <c r="G35" s="5">
+      <c r="F35" s="4">
         <v>781180552</v>
       </c>
+      <c r="G35" s="4">
+        <v>781180552</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F36" s="5">
-        <v>774790213</v>
-      </c>
-      <c r="G36" s="5">
+      <c r="F36" s="4">
         <v>787080588</v>
       </c>
+      <c r="G36" s="4">
+        <v>787080588</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F37" s="5">
-        <v>788780692</v>
-      </c>
-      <c r="G37" s="5">
+      <c r="F37" s="4">
         <v>789150406</v>
       </c>
+      <c r="G37" s="4">
+        <v>789150406</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="11" t="s">
         <v>156</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -1721,176 +1715,176 @@
         <v>145</v>
       </c>
       <c r="F38" s="3">
-        <v>777509848</v>
+        <v>771545210</v>
       </c>
       <c r="G38" s="3">
         <v>771545210</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F39" s="5">
-        <v>776919692</v>
-      </c>
-      <c r="G39" s="5">
+      <c r="F39" s="4">
         <v>773958904</v>
       </c>
+      <c r="G39" s="4">
+        <v>773958904</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F40" s="5">
-        <v>783008307</v>
-      </c>
-      <c r="G40" s="5">
+      <c r="F40" s="4">
         <v>776950987</v>
       </c>
+      <c r="G40" s="4">
+        <v>776950987</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F41" s="7">
-        <v>780123961</v>
-      </c>
-      <c r="G41" s="5">
+      <c r="F41" s="4">
         <v>781825193</v>
       </c>
+      <c r="G41" s="4">
+        <v>781825193</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F42" s="5">
-        <v>778679190</v>
+      <c r="F42" s="3">
+        <v>786180521</v>
       </c>
       <c r="G42" s="3">
         <v>786180521</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F43" s="5">
-        <v>771994713</v>
-      </c>
-      <c r="G43" s="5">
+      <c r="F43" s="4">
         <v>786183517</v>
       </c>
+      <c r="G43" s="4">
+        <v>786183517</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F44" s="5">
-        <v>784119644</v>
-      </c>
-      <c r="G44" s="5">
+      <c r="F44" s="4">
         <v>772118585</v>
       </c>
+      <c r="G44" s="4">
+        <v>772118585</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="5">
         <v>787389275</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="5">
         <v>787389275</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1917,121 +1911,121 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="9">
         <v>774981290</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="9">
         <v>775499999</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="13"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <v>776247047</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>776665352</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <v>775499999</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>781287163</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="11">
         <v>772579898</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <v>774317541</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <v>773316647</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="11">
         <v>775451818</v>
       </c>
     </row>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -343,30 +343,18 @@
     <t xml:space="preserve">ABDOU LAHAD </t>
   </si>
   <si>
-    <t>Pvt_tdc590013</t>
-  </si>
-  <si>
     <t>ALLA  SOW</t>
   </si>
   <si>
-    <t>Pvt_tdc590043</t>
-  </si>
-  <si>
     <t xml:space="preserve">ABIBOU  </t>
   </si>
   <si>
-    <t>Pvt_tdc590120</t>
-  </si>
-  <si>
     <t>BILALY</t>
   </si>
   <si>
     <t>BASSOUM</t>
   </si>
   <si>
-    <t>Pvt_tdc590016</t>
-  </si>
-  <si>
     <t xml:space="preserve">VIEUX </t>
   </si>
   <si>
@@ -500,6 +488,18 @@
   </si>
   <si>
     <t>pvt_tbogo1124</t>
+  </si>
+  <si>
+    <t>pvt_tdc590120</t>
+  </si>
+  <si>
+    <t>pvt_tdc590016</t>
+  </si>
+  <si>
+    <t>pvt_tdc590043</t>
+  </si>
+  <si>
+    <t>pvt_tdc590013</t>
   </si>
 </sst>
 </file>
@@ -518,6 +518,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1427,7 +1428,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>92</v>
@@ -1450,7 +1451,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>95</v>
@@ -1473,7 +1474,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>97</v>
@@ -1496,7 +1497,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>100</v>
@@ -1519,7 +1520,7 @@
         <v>103</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>104</v>
@@ -1528,7 +1529,7 @@
         <v>25</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="F30" s="3">
         <v>788255458</v>
@@ -1542,16 +1543,16 @@
         <v>103</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>66</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="F31" s="4">
         <v>789166919</v>
@@ -1565,16 +1566,16 @@
         <v>103</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="F32" s="4">
         <v>789151415</v>
@@ -1588,16 +1589,16 @@
         <v>103</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="F33" s="4">
         <v>789166998</v>
@@ -1611,16 +1612,16 @@
         <v>57</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F34" s="3">
         <v>781180310</v>
@@ -1634,16 +1635,16 @@
         <v>57</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F35" s="4">
         <v>781180552</v>
@@ -1657,16 +1658,16 @@
         <v>57</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F36" s="4">
         <v>787080588</v>
@@ -1680,16 +1681,16 @@
         <v>57</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F37" s="4">
         <v>789150406</v>
@@ -1700,19 +1701,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F38" s="3">
         <v>771545210</v>
@@ -1723,19 +1724,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="F39" s="4">
         <v>773958904</v>
@@ -1746,19 +1747,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>52</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F40" s="4">
         <v>776950987</v>
@@ -1769,19 +1770,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F41" s="4">
         <v>781825193</v>
@@ -1795,16 +1796,16 @@
         <v>19</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F42" s="3">
         <v>786180521</v>
@@ -1818,16 +1819,16 @@
         <v>19</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F43" s="4">
         <v>786183517</v>
@@ -1841,16 +1842,16 @@
         <v>19</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F44" s="4">
         <v>772118585</v>
@@ -1864,16 +1865,16 @@
         <v>19</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F45" s="5">
         <v>787389275</v>
@@ -1907,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1923,7 +1924,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>20</v>
@@ -1934,16 +1935,16 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>31</v>
@@ -1954,10 +1955,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C6" s="11">
         <v>776665352</v>
@@ -1965,7 +1966,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>45</v>
@@ -1976,10 +1977,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C8" s="11">
         <v>781287163</v>
@@ -1987,10 +1988,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C9" s="11">
         <v>772579898</v>
@@ -1998,7 +1999,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>58</v>
@@ -2009,7 +2010,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>69</v>
@@ -2020,10 +2021,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C12" s="11">
         <v>775451818</v>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -16,6 +16,10 @@
     <sheet name="pvt" sheetId="3" r:id="rId2"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Feuil2!$A$1:$B$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">vto!$A$1:$G$45</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -490,16 +494,16 @@
     <t>pvt_tbogo1124</t>
   </si>
   <si>
-    <t>pvt_tdc590120</t>
-  </si>
-  <si>
-    <t>pvt_tdc590016</t>
-  </si>
-  <si>
-    <t>pvt_tdc590043</t>
-  </si>
-  <si>
-    <t>pvt_tdc590013</t>
+    <t>Pvt_tdc590013</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590043</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590120</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590016</t>
   </si>
 </sst>
 </file>
@@ -1529,7 +1533,7 @@
         <v>25</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F30" s="3">
         <v>788255458</v>
@@ -1552,7 +1556,7 @@
         <v>66</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F31" s="4">
         <v>789166919</v>
@@ -1575,7 +1579,7 @@
         <v>22</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F32" s="4">
         <v>789151415</v>
@@ -1598,7 +1602,7 @@
         <v>108</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F33" s="4">
         <v>789166998</v>
@@ -1888,6 +1892,7 @@
       <c r="D53" s="11"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G45"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2247,6 +2252,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B25"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="164">
   <si>
     <t>DRV</t>
   </si>
@@ -71,12 +71,6 @@
     <t>pvt_tcg_0260</t>
   </si>
   <si>
-    <t>FAYE</t>
-  </si>
-  <si>
-    <t>MOUHAMATH</t>
-  </si>
-  <si>
     <t>pvt_tcg_0035</t>
   </si>
   <si>
@@ -95,9 +89,6 @@
     <t>PVT SERIGNE MBACKE MADINA CISSE (ZONE TOUBA)</t>
   </si>
   <si>
-    <t>ASSANE</t>
-  </si>
-  <si>
     <t>DIOP</t>
   </si>
   <si>
@@ -113,12 +104,6 @@
     <t>pvt_smmc301</t>
   </si>
   <si>
-    <t>MAYANE</t>
-  </si>
-  <si>
-    <t>NDIM</t>
-  </si>
-  <si>
     <t>pvt_smmc2695</t>
   </si>
   <si>
@@ -146,18 +131,9 @@
     <t>pvt_dfallf0271</t>
   </si>
   <si>
-    <t>AWA</t>
-  </si>
-  <si>
-    <t>NDOUR</t>
-  </si>
-  <si>
     <t>pvt_dfallf0272</t>
   </si>
   <si>
-    <t>IBRAHIMA</t>
-  </si>
-  <si>
     <t>DIALLO</t>
   </si>
   <si>
@@ -504,6 +480,48 @@
   </si>
   <si>
     <t>Pvt_tdc590016</t>
+  </si>
+  <si>
+    <t>pvt_dfallf0418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDEYE </t>
+  </si>
+  <si>
+    <t>pvt_dfallf0422</t>
+  </si>
+  <si>
+    <t>SAPHIE</t>
+  </si>
+  <si>
+    <t>pvt_dfallf0183</t>
+  </si>
+  <si>
+    <t>MOUSTAPHA</t>
+  </si>
+  <si>
+    <t>BABA</t>
+  </si>
+  <si>
+    <t>CISSE</t>
+  </si>
+  <si>
+    <t>pvt_tcg_0115</t>
+  </si>
+  <si>
+    <t>Pvt_smmc2921</t>
+  </si>
+  <si>
+    <t>NDEYE ANTA</t>
+  </si>
+  <si>
+    <t>Pvt_smmc2988</t>
+  </si>
+  <si>
+    <t>MOHAMET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                        </t>
   </si>
 </sst>
 </file>
@@ -611,7 +629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -641,6 +659,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -922,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
@@ -931,7 +952,7 @@
     <col min="5" max="5" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -948,10 +969,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -971,7 +992,7 @@
         <v>782989910</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -991,7 +1012,7 @@
         <v>787095594</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -999,19 +1020,19 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="F4">
         <v>781180981</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1019,349 +1040,359 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
       </c>
       <c r="F5">
         <v>787095584</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J5">
+        <v>789166714</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="F6">
         <v>786241266</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F7">
         <v>789160174</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F8">
         <v>786241255</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="F9">
         <v>775812208</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10">
+        <v>789166714</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F11" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12">
+        <v>789166702</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13">
+        <v>787655205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
         <v>34</v>
       </c>
-      <c r="F10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>36</v>
       </c>
-      <c r="E11" t="s">
+      <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="F11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C15" t="s">
         <v>40</v>
       </c>
-      <c r="F12">
-        <v>778528509</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D15" t="s">
         <v>41</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E15" t="s">
         <v>42</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F15" s="2">
+        <v>782974728</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
         <v>43</v>
       </c>
-      <c r="F13">
-        <v>787655222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="D16" t="s">
         <v>44</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E16" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" t="s">
-        <v>53</v>
-      </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" t="s">
-        <v>81</v>
+        <v>51</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
         <v>57</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
         <v>58</v>
       </c>
-      <c r="C21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" t="s">
-        <v>66</v>
-      </c>
       <c r="E21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="F21" s="2">
+        <v>789167632</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F22">
         <v>775810336</v>
@@ -1369,19 +1400,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F23">
         <v>778525987</v>
@@ -1389,19 +1420,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
         <v>68</v>
       </c>
-      <c r="B24" t="s">
+      <c r="E24" t="s">
         <v>69</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" t="s">
-        <v>77</v>
       </c>
       <c r="F24">
         <v>772104981</v>
@@ -1409,19 +1440,19 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F25">
         <v>772107591</v>
@@ -1429,19 +1460,19 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F26" s="3">
         <v>777410048</v>
@@ -1452,19 +1483,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F27" s="4">
         <v>787656877</v>
@@ -1475,19 +1506,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F28" s="4">
         <v>776019823</v>
@@ -1498,19 +1529,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F29" s="4">
         <v>782981141</v>
@@ -1521,19 +1552,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F30" s="3">
         <v>788255458</v>
@@ -1544,19 +1575,19 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F31" s="4">
         <v>789166919</v>
@@ -1567,19 +1598,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="F32" s="4">
         <v>789151415</v>
@@ -1590,19 +1621,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F33" s="4">
         <v>789166998</v>
@@ -1613,19 +1644,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F34" s="3">
         <v>781180310</v>
@@ -1636,19 +1667,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F35" s="4">
         <v>781180552</v>
@@ -1659,19 +1690,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F36" s="4">
         <v>787080588</v>
@@ -1682,19 +1713,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F37" s="4">
         <v>789150406</v>
@@ -1705,19 +1736,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F38" s="3">
         <v>771545210</v>
@@ -1728,19 +1759,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F39" s="4">
         <v>773958904</v>
@@ -1751,19 +1782,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F40" s="4">
         <v>776950987</v>
@@ -1774,19 +1805,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>128</v>
-      </c>
       <c r="E41" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F41" s="4">
         <v>781825193</v>
@@ -1797,19 +1828,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F42" s="3">
         <v>786180521</v>
@@ -1820,19 +1851,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B43" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="F43" s="4">
         <v>786183517</v>
@@ -1843,19 +1874,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F44" s="4">
         <v>772118585</v>
@@ -1866,19 +1897,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F45" s="5">
         <v>787389275</v>
@@ -1894,6 +1925,7 @@
   </sheetData>
   <autoFilter ref="A1:G45"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1913,7 +1945,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1929,10 +1961,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" s="9">
         <v>775499999</v>
@@ -1940,19 +1972,19 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C5" s="9">
         <v>776247047</v>
@@ -1960,10 +1992,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C6" s="11">
         <v>776665352</v>
@@ -1971,10 +2003,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C7" s="9">
         <v>775499999</v>
@@ -1982,10 +2014,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C8" s="11">
         <v>781287163</v>
@@ -1993,10 +2025,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C9" s="11">
         <v>772579898</v>
@@ -2004,10 +2036,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C10" s="9">
         <v>774317541</v>
@@ -2015,10 +2047,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C11" s="9">
         <v>773316647</v>
@@ -2026,10 +2058,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C12" s="11">
         <v>775451818</v>
@@ -2060,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -2081,7 +2113,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>781180981</v>
@@ -2089,7 +2121,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>787095584</v>
@@ -2097,7 +2129,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>786241266</v>
@@ -2105,7 +2137,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B7">
         <v>789160174</v>
@@ -2113,7 +2145,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>786241255</v>
@@ -2121,7 +2153,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>775812208</v>
@@ -2129,23 +2161,23 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>778528509</v>
@@ -2153,7 +2185,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>787655222</v>
@@ -2161,67 +2193,67 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B22">
         <v>775810336</v>
@@ -2229,7 +2261,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B23">
         <v>778525987</v>
@@ -2237,7 +2269,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B24">
         <v>772104981</v>
@@ -2245,7 +2277,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B25">
         <v>772107591</v>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="166">
   <si>
     <t>DRV</t>
   </si>
@@ -152,30 +152,18 @@
     <t>Pvt_mbpling0230</t>
   </si>
   <si>
-    <t>BAYE SALIOU</t>
-  </si>
-  <si>
     <t>DIAKHATE</t>
   </si>
   <si>
     <t>Pvt_mbpling009</t>
   </si>
   <si>
-    <t>DEMBA SOUMARE</t>
-  </si>
-  <si>
     <t>DIOUF</t>
   </si>
   <si>
     <t>Pvt_mbpling173</t>
   </si>
   <si>
-    <t>OUSSEYNOU</t>
-  </si>
-  <si>
-    <t>MBAYE</t>
-  </si>
-  <si>
     <t>Pvt_mbpling114</t>
   </si>
   <si>
@@ -522,6 +510,24 @@
   </si>
   <si>
     <t xml:space="preserve">                                                                                        </t>
+  </si>
+  <si>
+    <t>pvt_mbpling0274</t>
+  </si>
+  <si>
+    <t>MBENGUE</t>
+  </si>
+  <si>
+    <t>pvt_mbpling0268</t>
+  </si>
+  <si>
+    <t>NDEYE ASTOU</t>
+  </si>
+  <si>
+    <t>NDONGO</t>
+  </si>
+  <si>
+    <t>pvt_mbpling0193</t>
   </si>
 </sst>
 </file>
@@ -657,11 +663,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -948,7 +954,7 @@
   <cols>
     <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -969,7 +975,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
@@ -1020,13 +1026,13 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F4">
         <v>781180981</v>
@@ -1063,13 +1069,13 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" t="s">
         <v>157</v>
-      </c>
-      <c r="E6" t="s">
-        <v>161</v>
       </c>
       <c r="F6">
         <v>786241266</v>
@@ -1083,19 +1089,19 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F7">
         <v>789160174</v>
       </c>
       <c r="G7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -1126,13 +1132,13 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F9">
         <v>775812208</v>
@@ -1146,13 +1152,13 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F10">
         <v>789166714</v>
@@ -1174,8 +1180,8 @@
       <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>76</v>
+      <c r="F11" s="13" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -1186,13 +1192,13 @@
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F12">
         <v>789166702</v>
@@ -1206,13 +1212,13 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F13">
         <v>787655205</v>
@@ -1235,7 +1241,7 @@
         <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -1246,16 +1252,16 @@
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="2">
-        <v>782974728</v>
+        <v>162</v>
+      </c>
+      <c r="F15">
+        <v>787080726</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -1266,16 +1272,16 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" t="s">
-        <v>80</v>
+        <v>160</v>
+      </c>
+      <c r="F16">
+        <v>787081068</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1286,24 +1292,24 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>163</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" t="s">
-        <v>78</v>
+        <v>165</v>
+      </c>
+      <c r="F17">
+        <v>781590999</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -1312,67 +1318,67 @@
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>73</v>
+        <v>47</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
         <v>50</v>
       </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F21" s="2">
         <v>789167632</v>
@@ -1380,19 +1386,19 @@
     </row>
     <row r="22" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" t="s">
         <v>60</v>
-      </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" t="s">
-        <v>64</v>
       </c>
       <c r="F22">
         <v>775810336</v>
@@ -1400,19 +1406,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
         <v>61</v>
       </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F23">
         <v>778525987</v>
@@ -1420,19 +1426,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
         <v>61</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" t="s">
         <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" t="s">
-        <v>69</v>
       </c>
       <c r="F24">
         <v>772104981</v>
@@ -1440,19 +1446,19 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F25">
         <v>772107591</v>
@@ -1463,16 +1469,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F26" s="3">
         <v>777410048</v>
@@ -1486,16 +1492,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F27" s="4">
         <v>787656877</v>
@@ -1509,16 +1515,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F28" s="4">
         <v>776019823</v>
@@ -1532,16 +1538,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F29" s="4">
         <v>782981141</v>
@@ -1552,19 +1558,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F30" s="3">
         <v>788255458</v>
@@ -1575,19 +1581,19 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F31" s="4">
         <v>789166919</v>
@@ -1598,19 +1604,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F32" s="4">
         <v>789151415</v>
@@ -1621,19 +1627,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="D33" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F33" s="4">
         <v>789166998</v>
@@ -1644,19 +1650,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F34" s="3">
         <v>781180310</v>
@@ -1667,19 +1673,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F35" s="4">
         <v>781180552</v>
@@ -1690,19 +1696,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F36" s="4">
         <v>787080588</v>
@@ -1713,19 +1719,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F37" s="4">
         <v>789150406</v>
@@ -1736,19 +1742,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F38" s="3">
         <v>771545210</v>
@@ -1759,19 +1765,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="F39" s="4">
         <v>773958904</v>
@@ -1782,19 +1788,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F40" s="4">
         <v>776950987</v>
@@ -1805,19 +1811,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F41" s="4">
         <v>781825193</v>
@@ -1831,16 +1837,16 @@
         <v>17</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F42" s="3">
         <v>786180521</v>
@@ -1854,16 +1860,16 @@
         <v>17</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F43" s="4">
         <v>786183517</v>
@@ -1877,16 +1883,16 @@
         <v>17</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F44" s="4">
         <v>772118585</v>
@@ -1900,16 +1906,16 @@
         <v>17</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F45" s="5">
         <v>787389275</v>
@@ -1945,7 +1951,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1961,7 +1967,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>18</v>
@@ -1972,16 +1978,16 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>136</v>
+      <c r="A5" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>26</v>
@@ -1991,19 +1997,19 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
-        <v>136</v>
+      <c r="A6" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C6" s="11">
         <v>776665352</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
-        <v>139</v>
+      <c r="A7" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>37</v>
@@ -2013,55 +2019,55 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="13" t="s">
-        <v>139</v>
+      <c r="A8" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C8" s="11">
         <v>781287163</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="13" t="s">
-        <v>141</v>
+      <c r="A9" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C9" s="11">
         <v>772579898</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="13" t="s">
-        <v>141</v>
+      <c r="A10" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C10" s="9">
         <v>774317541</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
-        <v>143</v>
+      <c r="A11" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C11" s="9">
         <v>773316647</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="13" t="s">
-        <v>143</v>
+      <c r="A12" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C12" s="11">
         <v>775451818</v>
@@ -2092,7 +2098,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -2137,7 +2143,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B7">
         <v>789160174</v>
@@ -2164,7 +2170,7 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -2172,7 +2178,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -2196,64 +2202,64 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B22">
         <v>775810336</v>
@@ -2261,7 +2267,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B23">
         <v>778525987</v>
@@ -2269,7 +2275,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B24">
         <v>772104981</v>
@@ -2277,7 +2283,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B25">
         <v>772107591</v>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Feuil2!$A$1:$B$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">vto!$A$1:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">vto!$A$1:$F$45</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="161">
   <si>
     <t>DRV</t>
   </si>
@@ -83,9 +83,6 @@
     <t>pvt_tcg_0331</t>
   </si>
   <si>
-    <t>DR CENTRE</t>
-  </si>
-  <si>
     <t>PVT SERIGNE MBACKE MADINA CISSE (ZONE TOUBA)</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>pvt_dfallf0220</t>
   </si>
   <si>
-    <t>DR NORD</t>
-  </si>
-  <si>
     <t>PVT MADINA BUSINESS PRO (RAVT LINGUERE)</t>
   </si>
   <si>
@@ -167,9 +161,6 @@
     <t>Pvt_mbpling114</t>
   </si>
   <si>
-    <t>SUD EST</t>
-  </si>
-  <si>
     <t>PVT SEYDINA OUSMANE SY ( ZONE TAMBA)</t>
   </si>
   <si>
@@ -356,9 +347,6 @@
     <t>pvt_sfof0228</t>
   </si>
   <si>
-    <t xml:space="preserve">SUD </t>
-  </si>
-  <si>
     <t xml:space="preserve">BINTOU  </t>
   </si>
   <si>
@@ -507,9 +495,6 @@
   </si>
   <si>
     <t>MOHAMET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                                                        </t>
   </si>
   <si>
     <t>pvt_mbpling0274</t>
@@ -635,24 +620,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -663,8 +636,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -949,16 +942,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="10.90625" style="7"/>
     <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -975,961 +969,874 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5">
+        <v>782989910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="14"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="5">
+        <v>787095594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="14"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="5">
+        <v>781180981</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="15"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5">
+        <v>787095584</v>
+      </c>
+      <c r="I5">
+        <v>789166714</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="5">
+        <v>786241266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="14"/>
+      <c r="B7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="5">
+        <v>789160174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="14"/>
+      <c r="B8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="5">
+        <v>786241255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="15"/>
+      <c r="B9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" s="5">
+        <v>775812208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" s="5">
+        <v>789166714</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="14"/>
+      <c r="B11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="14"/>
+      <c r="B12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" s="5">
+        <v>789166702</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="15"/>
+      <c r="B13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="5">
+        <v>787655205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="14"/>
+      <c r="B15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" s="5">
+        <v>787080726</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="14"/>
+      <c r="B16" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" s="5">
+        <v>787081068</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="15"/>
+      <c r="B17" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" s="5">
+        <v>781590999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+      <c r="B19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="14"/>
+      <c r="B20" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>782989910</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>787095594</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F4">
-        <v>781180981</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5">
-        <v>787095584</v>
-      </c>
-      <c r="J5">
-        <v>789166714</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="15"/>
+      <c r="B21" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="9">
+        <v>789167632</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="5">
+        <v>775810336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="5">
+        <v>778525987</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="5">
+        <v>772104981</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="5">
+        <v>772107591</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="5">
+        <v>777410048</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="5">
+        <v>787656877</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="5">
+        <v>776019823</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="5">
+        <v>782981141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" s="5">
+        <v>788255458</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="5">
+        <v>789166919</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F6">
-        <v>786241266</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7">
-        <v>789160174</v>
-      </c>
-      <c r="G7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E32" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F32" s="5">
+        <v>789151415</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" s="5">
+        <v>789166998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="5">
+        <v>781180310</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="14"/>
+      <c r="B35" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F35" s="5">
+        <v>781180552</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="14"/>
+      <c r="B36" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="5">
+        <v>787080588</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="15"/>
+      <c r="B37" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" s="5">
+        <v>789150406</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>786241255</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F9">
-        <v>775812208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F10">
-        <v>789166714</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s">
-        <v>146</v>
-      </c>
-      <c r="F12">
-        <v>789166702</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E38" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F38" s="5">
+        <v>771545210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" s="5">
+        <v>773958904</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E13" t="s">
-        <v>150</v>
-      </c>
-      <c r="F13">
-        <v>787655205</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" t="s">
-        <v>161</v>
-      </c>
-      <c r="E15" t="s">
-        <v>162</v>
-      </c>
-      <c r="F15">
-        <v>787080726</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>126</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>160</v>
-      </c>
-      <c r="F16">
-        <v>787081068</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>163</v>
-      </c>
-      <c r="D17" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" t="s">
-        <v>165</v>
-      </c>
-      <c r="F17">
-        <v>781590999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="E40" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="5">
+        <v>776950987</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="2">
-        <v>789167632</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22">
-        <v>775810336</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23">
-        <v>778525987</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24">
-        <v>772104981</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25">
-        <v>772107591</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="3">
-        <v>777410048</v>
-      </c>
-      <c r="G26" s="3">
-        <v>777410048</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F27" s="4">
-        <v>787656877</v>
-      </c>
-      <c r="G27" s="4">
-        <v>787656877</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F28" s="4">
-        <v>776019823</v>
-      </c>
-      <c r="G28" s="4">
-        <v>776019823</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="4">
-        <v>782981141</v>
-      </c>
-      <c r="G29" s="4">
-        <v>782981141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="11" t="s">
+      <c r="B41" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F30" s="3">
-        <v>788255458</v>
-      </c>
-      <c r="G30" s="3">
-        <v>788255458</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F31" s="4">
-        <v>789166919</v>
-      </c>
-      <c r="G31" s="4">
-        <v>789166919</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F32" s="4">
-        <v>789151415</v>
-      </c>
-      <c r="G32" s="4">
-        <v>789151415</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F33" s="4">
-        <v>789166998</v>
-      </c>
-      <c r="G33" s="4">
-        <v>789166998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="3">
-        <v>781180310</v>
-      </c>
-      <c r="G34" s="3">
-        <v>781180310</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F35" s="4">
-        <v>781180552</v>
-      </c>
-      <c r="G35" s="4">
-        <v>781180552</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F36" s="4">
-        <v>787080588</v>
-      </c>
-      <c r="G36" s="4">
-        <v>787080588</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F37" s="4">
-        <v>789150406</v>
-      </c>
-      <c r="G37" s="4">
-        <v>789150406</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="C41" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="5">
+        <v>781825193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F38" s="3">
-        <v>771545210</v>
-      </c>
-      <c r="G38" s="3">
-        <v>771545210</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F39" s="4">
-        <v>773958904</v>
-      </c>
-      <c r="G39" s="4">
-        <v>773958904</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" s="4" t="s">
+      <c r="C42" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="4">
-        <v>776950987</v>
-      </c>
-      <c r="G40" s="4">
-        <v>776950987</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="F42" s="5">
+        <v>786180521</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="14"/>
+      <c r="B43" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F41" s="4">
-        <v>781825193</v>
-      </c>
-      <c r="G41" s="4">
-        <v>781825193</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C42" s="4" t="s">
+      <c r="D43" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="E43" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F43" s="5">
+        <v>786183517</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="14"/>
+      <c r="B44" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="D44" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F42" s="3">
-        <v>786180521</v>
-      </c>
-      <c r="G42" s="3">
-        <v>786180521</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" s="4" t="s">
+      <c r="E44" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="F44" s="5">
+        <v>772118585</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="15"/>
+      <c r="B45" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F43" s="4">
-        <v>786183517</v>
-      </c>
-      <c r="G43" s="4">
-        <v>786183517</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C44" s="4" t="s">
+      <c r="D45" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="E45" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F44" s="4">
-        <v>772118585</v>
-      </c>
-      <c r="G44" s="4">
-        <v>772118585</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="F45" s="5">
         <v>787389275</v>
       </c>
-      <c r="G45" s="5">
-        <v>787389275</v>
-      </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G45"/>
+  <autoFilter ref="A1:F45"/>
+  <mergeCells count="22">
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1951,125 +1858,125 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3">
+        <v>774981290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3">
+        <v>775499999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3">
+        <v>776247047</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="9">
-        <v>774981290</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="C6" s="5">
+        <v>776665352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="9">
+      <c r="B7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="3">
         <v>775499999</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B8" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="5">
+        <v>781287163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="11"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="9">
-        <v>776247047</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="B9" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="11">
-        <v>776665352</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
+      <c r="C9" s="5">
+        <v>772579898</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="3">
+        <v>774317541</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="9">
-        <v>775499999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
+      <c r="B11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="3">
+        <v>773316647</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B12" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="11">
-        <v>781287163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="11">
-        <v>772579898</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="9">
-        <v>774317541</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="9">
-        <v>773316647</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="11">
+      <c r="C12" s="5">
         <v>775451818</v>
       </c>
     </row>
@@ -2098,7 +2005,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -2135,7 +2042,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>786241266</v>
@@ -2143,7 +2050,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B7">
         <v>789160174</v>
@@ -2151,7 +2058,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>786241255</v>
@@ -2159,7 +2066,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>775812208</v>
@@ -2167,23 +2074,23 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <v>778528509</v>
@@ -2191,7 +2098,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>787655222</v>
@@ -2199,67 +2106,67 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B22">
         <v>775810336</v>
@@ -2267,7 +2174,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B23">
         <v>778525987</v>
@@ -2275,7 +2182,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B24">
         <v>772104981</v>
@@ -2283,7 +2190,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B25">
         <v>772107591</v>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="159">
   <si>
     <t>DRV</t>
   </si>
@@ -104,9 +104,6 @@
     <t>pvt_smmc2695</t>
   </si>
   <si>
-    <t>DR EST</t>
-  </si>
-  <si>
     <t>PVT DEMBA FALL ( RAVT ZONE FATICK)</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
     <t>pvt_sosy0560</t>
   </si>
   <si>
-    <t>DR SUD</t>
-  </si>
-  <si>
     <t>PVT MOR WADE (ZONE KOLDA)</t>
   </si>
   <si>
@@ -296,9 +290,6 @@
     <t>pvt_itrkaf192</t>
   </si>
   <si>
-    <t>NORD</t>
-  </si>
-  <si>
     <t xml:space="preserve">ABDOU LAHAD </t>
   </si>
   <si>
@@ -513,6 +504,9 @@
   </si>
   <si>
     <t>pvt_mbpling0193</t>
+  </si>
+  <si>
+    <t> 787657059</t>
   </si>
 </sst>
 </file>
@@ -556,7 +550,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -580,9 +574,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -593,9 +598,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -604,9 +607,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -636,32 +637,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,8 +944,8 @@
   <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="7"/>
-    <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="16"/>
+    <col min="2" max="2" width="58.90625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="15.08984375" bestFit="1" customWidth="1"/>
@@ -956,7 +955,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -969,14 +968,14 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -993,8 +992,12 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="14"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>6</v>
+      </c>
       <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
@@ -1009,24 +1012,32 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="14"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>6</v>
+      </c>
       <c r="C4" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F4" s="5">
         <v>781180981</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="15"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>6</v>
+      </c>
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
@@ -1044,46 +1055,50 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F6" s="5">
         <v>786241266</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="14"/>
-      <c r="B7" s="11" t="s">
+      <c r="A7" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="F7" s="5">
         <v>789160174</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="14"/>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -1100,300 +1115,320 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="15"/>
+      <c r="A9" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F9" s="5">
         <v>775812208</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>25</v>
+      <c r="A10" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F10" s="5">
         <v>789166714</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="14"/>
-      <c r="B11" s="11" t="s">
-        <v>25</v>
+      <c r="A11" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>69</v>
+      <c r="F11" s="7" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="14"/>
-      <c r="B12" s="11" t="s">
-        <v>25</v>
+      <c r="A12" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F12" s="5">
         <v>789166702</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="15"/>
+      <c r="A13" s="15" t="s">
+        <v>125</v>
+      </c>
       <c r="B13" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F13" s="5">
         <v>787655205</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" s="10" t="s">
+      <c r="A14" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="14"/>
-      <c r="B15" s="11" t="s">
-        <v>35</v>
+      <c r="A15" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F15" s="5">
         <v>787080726</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="14"/>
-      <c r="B16" s="11" t="s">
-        <v>35</v>
+      <c r="A16" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F16" s="5">
         <v>787081068</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="15"/>
+      <c r="A17" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="B17" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F17" s="5">
         <v>781590999</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="10" t="s">
+      <c r="A18" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="14"/>
-      <c r="B19" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="14"/>
-      <c r="B20" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="15"/>
-      <c r="B21" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="8">
+        <v>789167632</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="9">
-        <v>789167632</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="10" t="s">
+      <c r="C22" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="F22" s="5">
         <v>775810336</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>54</v>
+      <c r="A23" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="F23" s="5">
         <v>778525987</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>54</v>
+      <c r="A24" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F24" s="5">
         <v>772104981</v>
@@ -1401,79 +1436,79 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>54</v>
+        <v>132</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F25" s="5">
         <v>772107591</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>130</v>
+      <c r="A26" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="F26" s="5">
         <v>777410048</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>130</v>
+      <c r="A27" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>127</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F27" s="5">
         <v>787656877</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>130</v>
+      <c r="A28" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>127</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="F28" s="5">
         <v>776019823</v>
@@ -1481,79 +1516,79 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>127</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="F29" s="5">
         <v>782981141</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>132</v>
+      <c r="A30" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F30" s="5">
         <v>788255458</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>132</v>
+      <c r="A31" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F31" s="5">
         <v>789166919</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F32" s="5">
         <v>789151415</v>
@@ -1561,153 +1596,159 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F33" s="5">
         <v>789166998</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>134</v>
+      <c r="A34" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F34" s="5">
         <v>781180310</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="14"/>
-      <c r="B35" s="11" t="s">
-        <v>134</v>
+      <c r="A35" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F35" s="5">
         <v>781180552</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="14"/>
-      <c r="B36" s="11" t="s">
-        <v>134</v>
+      <c r="A36" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F36" s="5">
         <v>787080588</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="15"/>
-      <c r="B37" s="12" t="s">
-        <v>134</v>
+      <c r="A37" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>131</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F37" s="5">
         <v>789150406</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>136</v>
+      <c r="A38" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F38" s="5">
         <v>771545210</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>136</v>
+      <c r="A39" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>133</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F39" s="5">
         <v>773958904</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>136</v>
+      <c r="A40" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>133</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F40" s="5">
         <v>776950987</v>
@@ -1715,93 +1756,99 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>133</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F41" s="5">
         <v>781825193</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>129</v>
+      <c r="A42" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F42" s="5">
         <v>786180521</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="14"/>
-      <c r="B43" s="11" t="s">
-        <v>129</v>
+      <c r="A43" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>126</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F43" s="5">
         <v>786183517</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="14"/>
-      <c r="B44" s="11" t="s">
-        <v>129</v>
+      <c r="A44" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>126</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F44" s="5">
         <v>772118585</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="15"/>
-      <c r="B45" s="12" t="s">
-        <v>129</v>
+      <c r="A45" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>126</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F45" s="5">
         <v>787389275</v>
@@ -1813,30 +1860,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F45"/>
-  <mergeCells count="22">
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1858,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1874,7 +1897,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>17</v>
@@ -1885,96 +1908,96 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
-        <v>128</v>
+      <c r="A5" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3">
         <v>776247047</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
-        <v>128</v>
+      <c r="A6" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C6" s="5">
         <v>776665352</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
-        <v>131</v>
+      <c r="A7" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3">
         <v>775499999</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="16" t="s">
-        <v>131</v>
+      <c r="A8" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C8" s="5">
         <v>781287163</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
-        <v>133</v>
+      <c r="A9" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="5">
         <v>772579898</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
-        <v>133</v>
+      <c r="A10" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3">
         <v>774317541</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
-        <v>135</v>
+      <c r="A11" s="9" t="s">
+        <v>132</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" s="3">
         <v>773316647</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
-        <v>135</v>
+      <c r="A12" s="9" t="s">
+        <v>132</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C12" s="5">
         <v>775451818</v>
@@ -2005,7 +2028,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -2050,7 +2073,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7">
         <v>789160174</v>
@@ -2074,23 +2097,23 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12">
         <v>778528509</v>
@@ -2098,7 +2121,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>787655222</v>
@@ -2106,67 +2129,67 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <v>775810336</v>
@@ -2174,7 +2197,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B23">
         <v>778525987</v>
@@ -2182,7 +2205,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>772104981</v>
@@ -2190,7 +2213,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B25">
         <v>772107591</v>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -305,9 +305,6 @@
     <t>BASSOUM</t>
   </si>
   <si>
-    <t xml:space="preserve">VIEUX </t>
-  </si>
-  <si>
     <t>DANSOKHO</t>
   </si>
   <si>
@@ -507,6 +504,9 @@
   </si>
   <si>
     <t> 787657059</t>
+  </si>
+  <si>
+    <t>MADY</t>
   </si>
 </sst>
 </file>
@@ -641,9 +641,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -661,6 +658,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -944,8 +944,8 @@
   <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="16"/>
-    <col min="2" max="2" width="58.90625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="15"/>
+    <col min="2" max="2" width="58.90625" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="15.08984375" bestFit="1" customWidth="1"/>
@@ -955,7 +955,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -972,10 +972,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -992,10 +992,10 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -1012,30 +1012,30 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="F4" s="5">
         <v>781180981</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1055,30 +1055,30 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F6" s="5">
         <v>786241266</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1095,10 +1095,10 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="12" t="s">
+      <c r="A8" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -1115,50 +1115,50 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F9" s="5">
         <v>775812208</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F10" s="5">
         <v>789166714</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -1171,54 +1171,54 @@
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="12" t="s">
+      <c r="A12" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F12" s="5">
         <v>789166702</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F13" s="5">
         <v>787655205</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -1235,70 +1235,70 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>73</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="F15" s="5">
         <v>787080726</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B16" s="12" t="s">
+      <c r="A16" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F16" s="5">
         <v>787081068</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B17" s="12" t="s">
+      <c r="A17" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="F17" s="5">
         <v>781590999</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="12" t="s">
+      <c r="A18" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="5" t="s">
@@ -1315,10 +1315,10 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B19" s="13" t="s">
+      <c r="A19" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -1335,10 +1335,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B20" s="13" t="s">
+      <c r="A20" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="5" t="s">
@@ -1355,10 +1355,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -1375,10 +1375,10 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" s="12" t="s">
+      <c r="A22" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1395,10 +1395,10 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -1415,10 +1415,10 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B24" s="13" t="s">
+      <c r="A24" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1435,10 +1435,10 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B25" s="14" t="s">
+      <c r="A25" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>52</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -1455,11 +1455,11 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>127</v>
+      <c r="A26" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>75</v>
@@ -1475,11 +1475,11 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>127</v>
+      <c r="A27" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>78</v>
@@ -1495,11 +1495,11 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>127</v>
+      <c r="A28" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>80</v>
@@ -1515,11 +1515,11 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>127</v>
+      <c r="A29" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>126</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>83</v>
@@ -1535,11 +1535,11 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>129</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>86</v>
@@ -1548,18 +1548,18 @@
         <v>21</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F30" s="5">
         <v>788255458</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>87</v>
@@ -1568,18 +1568,18 @@
         <v>50</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F31" s="5">
         <v>789166919</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>88</v>
@@ -1588,18 +1588,18 @@
         <v>18</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F32" s="5">
         <v>789151415</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>129</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>89</v>
@@ -1608,247 +1608,247 @@
         <v>90</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F33" s="5">
         <v>789166998</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>131</v>
-      </c>
       <c r="C34" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="F34" s="5">
         <v>781180310</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="C35" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="F35" s="5">
         <v>781180552</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B36" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="C36" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="F36" s="5">
         <v>787080588</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>131</v>
-      </c>
       <c r="C37" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" s="5">
         <v>789150406</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>133</v>
-      </c>
       <c r="C38" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F38" s="5">
         <v>771545210</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="C39" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="F39" s="5">
         <v>773958904</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="C40" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F40" s="5">
         <v>776950987</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>133</v>
-      </c>
       <c r="C41" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="F41" s="5">
         <v>781825193</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>126</v>
+      <c r="A42" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="C42" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="F42" s="5">
         <v>786180521</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>126</v>
+      <c r="A43" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C43" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="E43" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F43" s="5">
         <v>786183517</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>126</v>
+      <c r="A44" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C44" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="F44" s="5">
         <v>772118585</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>126</v>
+      <c r="A45" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>125</v>
       </c>
       <c r="C45" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="F45" s="5">
         <v>787389275</v>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1897,7 +1897,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>17</v>
@@ -1908,16 +1908,16 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
         <v>124</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>24</v>
@@ -1927,19 +1927,19 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>125</v>
+      <c r="A6" s="16" t="s">
+        <v>124</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" s="5">
         <v>776665352</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>128</v>
+      <c r="A7" s="16" t="s">
+        <v>127</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>34</v>
@@ -1949,30 +1949,30 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="C8" s="5">
         <v>781287163</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="C9" s="5">
         <v>772579898</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>130</v>
+      <c r="A10" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>42</v>
@@ -1982,8 +1982,8 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>132</v>
+      <c r="A11" s="16" t="s">
+        <v>131</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>52</v>
@@ -1993,11 +1993,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="C12" s="5">
         <v>775451818</v>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="7010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="7010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="vto" sheetId="1" r:id="rId1"/>
@@ -635,9 +635,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -658,6 +655,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -944,8 +944,8 @@
   <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="15"/>
-    <col min="2" max="2" width="58.90625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="14"/>
+    <col min="2" max="2" width="58.90625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="15.08984375" bestFit="1" customWidth="1"/>
@@ -955,7 +955,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -972,10 +972,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -992,10 +992,10 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -1012,10 +1012,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -1032,10 +1032,10 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1055,10 +1055,10 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1075,10 +1075,10 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1095,10 +1095,10 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -1115,10 +1115,10 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -1135,10 +1135,10 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -1155,10 +1155,10 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -1170,15 +1170,15 @@
       <c r="E11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -1195,10 +1195,10 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -1215,10 +1215,10 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -1235,10 +1235,10 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -1255,10 +1255,10 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -1275,10 +1275,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -1295,10 +1295,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>42</v>
       </c>
       <c r="C18" s="5" t="s">
@@ -1310,15 +1310,15 @@
       <c r="E18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -1335,10 +1335,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="5" t="s">
@@ -1355,10 +1355,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -1370,15 +1370,15 @@
       <c r="E21" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="7">
         <v>789167632</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1395,10 +1395,10 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -1415,10 +1415,10 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1435,10 +1435,10 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -1455,10 +1455,10 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>126</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -1475,10 +1475,10 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="11" t="s">
         <v>126</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1495,10 +1495,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="11" t="s">
         <v>126</v>
       </c>
       <c r="C28" s="5" t="s">
@@ -1515,10 +1515,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="12" t="s">
         <v>126</v>
       </c>
       <c r="C29" s="5" t="s">
@@ -1535,10 +1535,10 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="10" t="s">
         <v>128</v>
       </c>
       <c r="C30" s="5" t="s">
@@ -1555,10 +1555,10 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="11" t="s">
         <v>128</v>
       </c>
       <c r="C31" s="5" t="s">
@@ -1575,10 +1575,10 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="11" t="s">
         <v>128</v>
       </c>
       <c r="C32" s="5" t="s">
@@ -1595,10 +1595,10 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="12" t="s">
         <v>128</v>
       </c>
       <c r="C33" s="5" t="s">
@@ -1615,10 +1615,10 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>130</v>
       </c>
       <c r="C34" s="5" t="s">
@@ -1635,10 +1635,10 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="11" t="s">
         <v>130</v>
       </c>
       <c r="C35" s="5" t="s">
@@ -1655,10 +1655,10 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="11" t="s">
         <v>130</v>
       </c>
       <c r="C36" s="5" t="s">
@@ -1675,10 +1675,10 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="12" t="s">
         <v>130</v>
       </c>
       <c r="C37" s="5" t="s">
@@ -1695,10 +1695,10 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="10" t="s">
         <v>132</v>
       </c>
       <c r="C38" s="5" t="s">
@@ -1715,10 +1715,10 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="11" t="s">
         <v>132</v>
       </c>
       <c r="C39" s="5" t="s">
@@ -1735,10 +1735,10 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="11" t="s">
         <v>132</v>
       </c>
       <c r="C40" s="5" t="s">
@@ -1755,10 +1755,10 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C41" s="5" t="s">
@@ -1775,10 +1775,10 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="10" t="s">
         <v>125</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -1795,10 +1795,10 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="11" t="s">
         <v>125</v>
       </c>
       <c r="C43" s="5" t="s">
@@ -1815,10 +1815,10 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="11" t="s">
         <v>125</v>
       </c>
       <c r="C44" s="5" t="s">
@@ -1835,10 +1835,10 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="12" t="s">
         <v>125</v>
       </c>
       <c r="C45" s="5" t="s">
@@ -1896,7 +1896,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="15" t="s">
         <v>123</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -1907,7 +1907,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="15" t="s">
         <v>123</v>
       </c>
       <c r="B4" s="5" t="s">

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -1913,7 +1913,9 @@
       <c r="B4" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="5">
+        <v>775945699</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="7010" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="7010"/>
   </bookViews>
   <sheets>
     <sheet name="vto" sheetId="1" r:id="rId1"/>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\Dossier LOUMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_46CBBBEB4BD4E64F51C9DC61FC2C65EABA356C5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8C612E-D71E-46E2-9297-A76DBD35E99B}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03BA07B5-901B-4853-B0CA-B793FC06C583}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Liste VTO" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste VTO'!$A$1:$F$49</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
   <si>
     <t>DRV</t>
   </si>
@@ -44,7 +47,16 @@
     <t>PVT</t>
   </si>
   <si>
-    <t>CONTACT</t>
+    <t>PRENOM_VENDEUR</t>
+  </si>
+  <si>
+    <t>NOM_VENDEUR</t>
+  </si>
+  <si>
+    <t>LOGIN</t>
+  </si>
+  <si>
+    <t>KABBU</t>
   </si>
   <si>
     <t>DR2</t>
@@ -53,59 +65,467 @@
     <t>PVT TEKNICOM CONSULTING GROUPE (SADI RUFISQUE-DIAMNIADIO)</t>
   </si>
   <si>
+    <t>AMDY</t>
+  </si>
+  <si>
+    <t>GUEYE</t>
+  </si>
+  <si>
+    <t>pvt_tcg_0124</t>
+  </si>
+  <si>
+    <t>FATOU</t>
+  </si>
+  <si>
+    <t>TAMBASSA</t>
+  </si>
+  <si>
+    <t>pvt_tcg_0260</t>
+  </si>
+  <si>
+    <t>BABA</t>
+  </si>
+  <si>
+    <t>CISSE</t>
+  </si>
+  <si>
+    <t>pvt_tcg_0115</t>
+  </si>
+  <si>
+    <t>SERIGNE FALLOU</t>
+  </si>
+  <si>
+    <t>BITEYE</t>
+  </si>
+  <si>
+    <t>pvt_tcg_0331</t>
+  </si>
+  <si>
     <t>IBRAHIMA SENE(SADI ZPPG)</t>
   </si>
   <si>
+    <t xml:space="preserve">KHADIM </t>
+  </si>
+  <si>
+    <t>NIANG</t>
+  </si>
+  <si>
+    <t>Pvt_ibsen0464</t>
+  </si>
+  <si>
+    <t>CHEIKH</t>
+  </si>
+  <si>
+    <t>DIOP</t>
+  </si>
+  <si>
+    <t>Pvt_ibsen0440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOUSSO </t>
+  </si>
+  <si>
+    <t>BADIANE</t>
+  </si>
+  <si>
+    <t>Pvt_ibsen0253</t>
+  </si>
+  <si>
+    <t>MAIMOUNA</t>
+  </si>
+  <si>
+    <t>CAMARA</t>
+  </si>
+  <si>
+    <t>Pvt_ibsen0239</t>
+  </si>
+  <si>
     <t>DRC</t>
   </si>
   <si>
     <t>PVT SERIGNE MBACKE MADINA CISSE (ZONE TOUBA)</t>
   </si>
   <si>
+    <t>MOHAMET</t>
+  </si>
+  <si>
+    <t>Pvt_smmc2988</t>
+  </si>
+  <si>
+    <t>MODOU</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>pvt_smmc2928</t>
+  </si>
+  <si>
+    <t>GAMOU</t>
+  </si>
+  <si>
+    <t>NDIAYE</t>
+  </si>
+  <si>
+    <t>pvt_smmc301</t>
+  </si>
+  <si>
+    <t>NDEYE ANTA</t>
+  </si>
+  <si>
+    <t>Pvt_smmc2921</t>
+  </si>
+  <si>
+    <t>DRE</t>
+  </si>
+  <si>
+    <t>PVT DEMBA FALL ( RAVT ZONE FATICK)</t>
+  </si>
+  <si>
+    <t>SAPHIE</t>
+  </si>
+  <si>
+    <t>DABO</t>
+  </si>
+  <si>
+    <t>pvt_dfallf0422</t>
+  </si>
+  <si>
+    <t>AMY</t>
+  </si>
+  <si>
+    <t>SAMB</t>
+  </si>
+  <si>
+    <t>pvt_dfallf0271</t>
+  </si>
+  <si>
+    <t> 787657059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDEYE </t>
+  </si>
+  <si>
+    <t>pvt_dfallf0418</t>
+  </si>
+  <si>
+    <t>MOUSTAPHA</t>
+  </si>
+  <si>
+    <t>DIAKHATE</t>
+  </si>
+  <si>
+    <t>pvt_dfallf0183</t>
+  </si>
+  <si>
+    <t>DRN</t>
+  </si>
+  <si>
+    <t>PVT MADINA BUSINESS PRO (RAVT LINGUERE)</t>
+  </si>
+  <si>
+    <t>ALIOUNE</t>
+  </si>
+  <si>
+    <t>DIALLO</t>
+  </si>
+  <si>
+    <t>Pvt_mbpling0230</t>
+  </si>
+  <si>
+    <t> 787095625</t>
+  </si>
+  <si>
+    <t>MBENGUE</t>
+  </si>
+  <si>
+    <t>pvt_mbpling0268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fallou </t>
+  </si>
+  <si>
+    <t>pvt_mbpling0274</t>
+  </si>
+  <si>
+    <t>NDEYE ASTOU</t>
+  </si>
+  <si>
+    <t>NDONGO</t>
+  </si>
+  <si>
+    <t>pvt_mbpling0193</t>
+  </si>
+  <si>
+    <t>DRSE</t>
+  </si>
+  <si>
+    <t>PVT SEYDINA OUSMANE SY ( ZONE TAMBA)</t>
+  </si>
+  <si>
+    <t>ABDOULAYE</t>
+  </si>
+  <si>
+    <t>pvt_sosy134</t>
+  </si>
+  <si>
+    <t> 771883753</t>
+  </si>
+  <si>
+    <t>DIOR</t>
+  </si>
+  <si>
+    <t>pvt_sosy0290</t>
+  </si>
+  <si>
+    <t> 775801980</t>
+  </si>
+  <si>
+    <t>KHADIDIATOU</t>
+  </si>
+  <si>
+    <t>SOUARE</t>
+  </si>
+  <si>
+    <t>pvt_sosy165</t>
+  </si>
+  <si>
+    <t> 781596632</t>
+  </si>
+  <si>
+    <t>MAHAMADOU</t>
+  </si>
+  <si>
+    <t>SOW</t>
+  </si>
+  <si>
+    <t>pvt_sosy0560</t>
+  </si>
+  <si>
+    <t>DRS</t>
+  </si>
+  <si>
+    <t>PVT MOR WADE (ZONE KOLDA)</t>
+  </si>
+  <si>
+    <t>FATOUMATA BINTA</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>pvt_mwadk0290</t>
+  </si>
+  <si>
+    <t>DR SUD</t>
+  </si>
+  <si>
+    <t>HAMADOU</t>
+  </si>
+  <si>
+    <t>BALDE</t>
+  </si>
+  <si>
+    <t>pvt_mwadk236</t>
+  </si>
+  <si>
+    <t>MBALLO</t>
+  </si>
+  <si>
+    <t>pvt_mwadk181</t>
+  </si>
+  <si>
+    <t>MOUHAMADOU KALIDOU</t>
+  </si>
+  <si>
+    <t>pvt_mwadk194</t>
+  </si>
+  <si>
+    <t>PVT ITR (ZONE KAFFRINE)</t>
+  </si>
+  <si>
+    <t>SEYNABOU</t>
+  </si>
+  <si>
+    <t>GAYE</t>
+  </si>
+  <si>
+    <t>pvt_itrkaf255</t>
+  </si>
+  <si>
+    <t>DR EST</t>
+  </si>
+  <si>
+    <t>PAPE ABDOULAYE</t>
+  </si>
+  <si>
+    <t>pvt_itrkaf0585</t>
+  </si>
+  <si>
+    <t>ROKY</t>
+  </si>
+  <si>
+    <t>KEBE</t>
+  </si>
+  <si>
+    <t>pvt_itrkaf292</t>
+  </si>
+  <si>
+    <t>OUSMANE</t>
+  </si>
+  <si>
+    <t>THIALL</t>
+  </si>
+  <si>
+    <t>pvt_itrkaf192</t>
+  </si>
+  <si>
+    <t>PVT Thomas Djibril Ciss (RAVT KEBEMER)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABDOU LAHAD </t>
+  </si>
+  <si>
+    <t>Pvt_tdc590013</t>
+  </si>
+  <si>
+    <t>NORD</t>
+  </si>
+  <si>
+    <t>ALLA  SOW</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABIBOU  </t>
+  </si>
+  <si>
+    <t>Pvt_tdc590120</t>
+  </si>
+  <si>
+    <t>BILALY</t>
+  </si>
+  <si>
+    <t>BASSOUM</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590016</t>
+  </si>
+  <si>
+    <t>PVT FOFANA SORIKE KEDOUGOU (RAVT ZONE KEDOUGOU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIEUX </t>
+  </si>
+  <si>
+    <t>DANSOKHO</t>
+  </si>
+  <si>
+    <t>pvt_sfof126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARIDIATOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DIALLO</t>
+  </si>
+  <si>
+    <t>pvt_sfof097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MADIALANG </t>
+  </si>
+  <si>
+    <t>DRAME</t>
+  </si>
+  <si>
+    <t>pvt_sfof0211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMADOU THIERNO </t>
+  </si>
+  <si>
+    <t>pvt_sfof0228</t>
+  </si>
+  <si>
+    <t>PVT ZIG TELECOM (RAVT ZIGUINCHOR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BINTOU  </t>
+  </si>
+  <si>
+    <t>pvt_zigtel_ravt_zig068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEAN EMMANUEL CHRISTOPHOR </t>
+  </si>
+  <si>
+    <t>BADJI</t>
+  </si>
+  <si>
+    <t>pvt_zigtel0351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FATOU </t>
+  </si>
+  <si>
+    <t>DIOUF</t>
+  </si>
+  <si>
+    <t>pvt_zigtel0316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDEYE FATOU  </t>
+  </si>
+  <si>
+    <t>MANE</t>
+  </si>
+  <si>
+    <t>pvt_zigtel281</t>
+  </si>
+  <si>
     <t>PVT TOUBA BOGO COMMUNICATION (ZONE MBOUR)</t>
   </si>
   <si>
-    <t>DRE</t>
-  </si>
-  <si>
-    <t>PVT DEMBA FALL ( RAVT ZONE FATICK)</t>
-  </si>
-  <si>
-    <t>PVT ITR (ZONE KAFFRINE)</t>
-  </si>
-  <si>
-    <t>DRN</t>
-  </si>
-  <si>
-    <t>PVT MADINA BUSINESS PRO (RAVT LINGUERE)</t>
-  </si>
-  <si>
-    <t>PVT Thomas Djibril Ciss (RAVT KEBEMER)</t>
-  </si>
-  <si>
-    <t>DRSE</t>
-  </si>
-  <si>
-    <t>PVT FOFANA SORIKE KEDOUGOU (RAVT ZONE KEDOUGOU)</t>
-  </si>
-  <si>
-    <t>PVT SEYDINA OUSMANE SY ( ZONE TAMBA)</t>
-  </si>
-  <si>
-    <t>DRS</t>
-  </si>
-  <si>
-    <t>PVT MOR WADE (ZONE KOLDA)</t>
-  </si>
-  <si>
-    <t>PVT ZIG TELECOM (RAVT ZIGUINCHOR)</t>
+    <t xml:space="preserve">Gnima </t>
+  </si>
+  <si>
+    <t>Diatta</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1367</t>
+  </si>
+  <si>
+    <t>Rose Mendy</t>
+  </si>
+  <si>
+    <t>Mendy</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pauline coumba </t>
+  </si>
+  <si>
+    <t>Faye</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1534</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1719</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,7 +536,16 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -125,15 +554,21 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -156,23 +591,211 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,14 +1076,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,140 +1096,1013 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3">
-        <v>774981290</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3">
-        <v>776647468</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15">
-      <c r="A4" s="4" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
-        <v>775499999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15">
-      <c r="A5" s="4" t="s">
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2">
+        <v>782989910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A3" s="11"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2">
+        <v>787095594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="11"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2">
+        <v>781180981</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="12"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2">
+        <v>787095584</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
-        <v>775945699</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15">
-      <c r="A6" s="4" t="s">
+      <c r="B6" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="8">
+        <v>785249423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="24"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="8">
+        <v>784720703</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A8" s="24"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="8">
+        <v>787979910</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A9" s="25"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="8">
+        <v>789514893</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="2">
+        <v>786241266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="11"/>
+      <c r="B11" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="2">
+        <v>789160174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="11"/>
+      <c r="B12" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2">
+        <v>786241255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="12"/>
+      <c r="B13" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3">
-        <v>776247047</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15">
-      <c r="A7" s="4" t="s">
+      <c r="E13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="2">
+        <v>775812208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="2">
+        <v>789166714</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="11"/>
+      <c r="B15" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="11"/>
+      <c r="B16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2">
-        <v>776665352</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15">
-      <c r="A8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3">
-        <v>775499999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2">
-        <v>781287163</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2">
-        <v>772579898</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15">
-      <c r="A11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="3">
-        <v>774317541</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="3">
-        <v>773316647</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="2">
+        <v>789166702</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="12"/>
+      <c r="B17" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="2">
+        <v>787655205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="11"/>
+      <c r="B19" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="2">
+        <v>787080726</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="11"/>
+      <c r="B20" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="2">
+        <v>787081068</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="12"/>
+      <c r="B21" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="2">
+        <v>781590999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="11"/>
+      <c r="B23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="11"/>
+      <c r="B24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="12"/>
+      <c r="B25" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="4">
+        <v>789167632</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="2">
+        <v>775810336</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="2">
+        <v>778525987</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" s="2">
+        <v>772104981</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="2">
+        <v>772107591</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="2">
+        <v>777410048</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="2">
+        <v>787656877</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" s="2">
+        <v>776019823</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="2">
+        <v>782981141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F34" s="2">
+        <v>788255458</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" s="2">
+        <v>789166919</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" s="2">
+        <v>789151415</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="2">
+        <v>789166998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" s="2">
+        <v>781180310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="11"/>
+      <c r="B39" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" s="2">
+        <v>781180552</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="11"/>
+      <c r="B40" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" s="2">
+        <v>787080588</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="12"/>
+      <c r="B41" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F41" s="2">
+        <v>789150406</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A42" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="2">
+        <v>771545210</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A43" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F43" s="2">
+        <v>773958904</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A44" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" s="2">
+        <v>776950987</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A45" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F45" s="2">
+        <v>781825193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F46" s="2">
+        <v>786180521</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="6"/>
+      <c r="B47" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F47" s="2">
+        <v>786183517</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="6"/>
+      <c r="B48" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F48" s="2">
+        <v>772118585</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="6"/>
+      <c r="B49" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="9">
+        <v>787389275</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="2">
-        <v>775451818</v>
+      <c r="C50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" s="8">
+        <v>785249423</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="20"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51" s="8">
+        <v>784720703</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="20"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" s="8">
+        <v>787979910</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="21"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" s="8">
+        <v>789514893</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="25">
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\Dossier LOUMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03BA07B5-901B-4853-B0CA-B793FC06C583}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60AF6145-723E-4584-AC1F-01138DCA7977}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -568,7 +568,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -680,55 +680,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -747,6 +703,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -756,14 +718,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -774,28 +739,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1107,10 +1056,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1127,8 +1076,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A3" s="11"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="11"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1143,8 +1092,8 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="11"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1159,29 +1108,29 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="12"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="13"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="9">
         <v>787095584</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -1195,9 +1144,9 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="24"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="26" t="s">
+      <c r="A7" s="22"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -1211,9 +1160,9 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A8" s="24"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="26" t="s">
+      <c r="A8" s="22"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="8" t="s">
@@ -1227,9 +1176,9 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="26" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="8" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="8" t="s">
@@ -1243,10 +1192,10 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1263,8 +1212,8 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="11"/>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="13"/>
+      <c r="B11" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1281,8 +1230,8 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="11"/>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="13"/>
+      <c r="B12" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1299,7 +1248,7 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="12"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
         <v>34</v>
       </c>
@@ -1317,10 +1266,10 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="10" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1337,8 +1286,8 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="11"/>
-      <c r="B15" s="14" t="s">
+      <c r="A15" s="13"/>
+      <c r="B15" s="11" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1355,8 +1304,8 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="11"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="13"/>
+      <c r="B16" s="11" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1373,7 +1322,7 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="12"/>
+      <c r="A17" s="14"/>
       <c r="B17" s="15" t="s">
         <v>46</v>
       </c>
@@ -1391,10 +1340,10 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="10" t="s">
         <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1411,8 +1360,8 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="11"/>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="13"/>
+      <c r="B19" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1429,8 +1378,8 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="11"/>
-      <c r="B20" s="14" t="s">
+      <c r="A20" s="13"/>
+      <c r="B20" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1447,7 +1396,7 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="12"/>
+      <c r="A21" s="14"/>
       <c r="B21" s="15" t="s">
         <v>60</v>
       </c>
@@ -1465,10 +1414,10 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="10" t="s">
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1485,8 +1434,8 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="11"/>
-      <c r="B23" s="14" t="s">
+      <c r="A23" s="13"/>
+      <c r="B23" s="11" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1503,8 +1452,8 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="11"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="13"/>
+      <c r="B24" s="11" t="s">
         <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1521,7 +1470,7 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="12"/>
+      <c r="A25" s="14"/>
       <c r="B25" s="15" t="s">
         <v>73</v>
       </c>
@@ -1539,10 +1488,10 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1559,10 +1508,10 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="11" t="s">
         <v>88</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -1579,10 +1528,10 @@
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="11" t="s">
         <v>88</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -1599,7 +1548,7 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="14" t="s">
         <v>92</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -1619,10 +1568,10 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="10" t="s">
         <v>100</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -1639,10 +1588,10 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="11" t="s">
         <v>100</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -1659,10 +1608,10 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="11" t="s">
         <v>100</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -1679,7 +1628,7 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="14" t="s">
         <v>104</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -1699,10 +1648,10 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="10" t="s">
         <v>113</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -1719,10 +1668,10 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="11" t="s">
         <v>113</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -1739,10 +1688,10 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="11" t="s">
         <v>113</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -1759,7 +1708,7 @@
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="14" t="s">
         <v>116</v>
       </c>
       <c r="B37" s="15" t="s">
@@ -1778,11 +1727,11 @@
         <v>789166998</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="10" t="s">
+    <row r="38" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A38" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="10" t="s">
         <v>124</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -1798,9 +1747,9 @@
         <v>781180310</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="11"/>
-      <c r="B39" s="14" t="s">
+    <row r="39" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A39" s="13"/>
+      <c r="B39" s="11" t="s">
         <v>124</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -1816,9 +1765,9 @@
         <v>781180552</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="11"/>
-      <c r="B40" s="14" t="s">
+    <row r="40" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A40" s="13"/>
+      <c r="B40" s="11" t="s">
         <v>124</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -1834,8 +1783,8 @@
         <v>787080588</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="12"/>
+    <row r="41" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A41" s="14"/>
       <c r="B41" s="15" t="s">
         <v>124</v>
       </c>
@@ -1852,11 +1801,11 @@
         <v>789150406</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A42" s="10" t="s">
+    <row r="42" spans="1:6">
+      <c r="A42" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="10" t="s">
         <v>136</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -1872,11 +1821,11 @@
         <v>771545210</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A43" s="11" t="s">
+    <row r="43" spans="1:6">
+      <c r="A43" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="11" t="s">
         <v>136</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -1892,11 +1841,11 @@
         <v>773958904</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A44" s="11" t="s">
+    <row r="44" spans="1:6">
+      <c r="A44" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="11" t="s">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -1912,8 +1861,8 @@
         <v>776950987</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A45" s="12" t="s">
+    <row r="45" spans="1:6">
+      <c r="A45" s="14" t="s">
         <v>92</v>
       </c>
       <c r="B45" s="15" t="s">
@@ -1936,7 +1885,7 @@
       <c r="A46" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="10" t="s">
         <v>148</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -1954,7 +1903,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="6"/>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="11" t="s">
         <v>148</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -1972,7 +1921,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6"/>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="11" t="s">
         <v>148</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -1990,7 +1939,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6"/>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="11" t="s">
         <v>148</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -2007,10 +1956,10 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="19" t="s">
+      <c r="A50" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="19" t="s">
         <v>20</v>
       </c>
       <c r="C50" s="8" t="s">
@@ -2027,8 +1976,8 @@
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="20"/>
-      <c r="B51" s="17"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="20"/>
       <c r="C51" s="8" t="s">
         <v>24</v>
       </c>
@@ -2043,8 +1992,8 @@
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="20"/>
-      <c r="B52" s="17"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="20"/>
       <c r="C52" s="8" t="s">
         <v>27</v>
       </c>
@@ -2059,8 +2008,8 @@
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="21"/>
-      <c r="B53" s="18"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="21"/>
       <c r="C53" s="8" t="s">
         <v>30</v>
       </c>
@@ -2077,15 +2026,8 @@
   </sheetData>
   <autoFilter ref="A1:F49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="25">
+    <mergeCell ref="B6:B9"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B38:B41"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="A2:A5"/>
@@ -2102,6 +2044,13 @@
     <mergeCell ref="B26:B29"/>
     <mergeCell ref="A42:A45"/>
     <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:B41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\Dossier LOUMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60AF6145-723E-4584-AC1F-01138DCA7977}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BEF439B-869A-4A3F-AE9E-B46D81BD02E6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -320,13 +320,13 @@
     <t>DR SUD</t>
   </si>
   <si>
+    <t xml:space="preserve">COUMBA </t>
+  </si>
+  <si>
+    <t>pvt_mwadk173</t>
+  </si>
+  <si>
     <t>HAMADOU</t>
-  </si>
-  <si>
-    <t>BALDE</t>
-  </si>
-  <si>
-    <t>pvt_mwadk236</t>
   </si>
   <si>
     <t>MBALLO</t>
@@ -703,22 +703,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -739,10 +727,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1056,10 +1056,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1076,8 +1076,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1092,8 +1092,8 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="13"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1108,8 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="13"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
@@ -1124,10 +1124,10 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1144,8 +1144,8 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="22"/>
-      <c r="B7" s="23"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="8" t="s">
         <v>24</v>
       </c>
@@ -1160,8 +1160,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A8" s="22"/>
-      <c r="B8" s="23"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="8" t="s">
         <v>27</v>
       </c>
@@ -1176,8 +1176,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="8" t="s">
         <v>30</v>
       </c>
@@ -1192,10 +1192,10 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1212,8 +1212,8 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="13"/>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1230,8 +1230,8 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="13"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1248,8 +1248,8 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="23" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1266,10 +1266,10 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="20" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1286,8 +1286,8 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="13"/>
-      <c r="B15" s="11" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="21" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1304,8 +1304,8 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="13"/>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="21" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1322,8 +1322,8 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15" t="s">
+      <c r="A17" s="22"/>
+      <c r="B17" s="23" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1340,10 +1340,10 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="20" t="s">
         <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1360,8 +1360,8 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="13"/>
-      <c r="B19" s="11" t="s">
+      <c r="A19" s="19"/>
+      <c r="B19" s="21" t="s">
         <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1378,8 +1378,8 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="13"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="19"/>
+      <c r="B20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1396,8 +1396,8 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="23" t="s">
         <v>60</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1414,10 +1414,10 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="20" t="s">
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1434,8 +1434,8 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="13"/>
-      <c r="B23" s="11" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1452,8 +1452,8 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="13"/>
-      <c r="B24" s="11" t="s">
+      <c r="A24" s="19"/>
+      <c r="B24" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1470,8 +1470,8 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="14"/>
-      <c r="B25" s="15" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="23" t="s">
         <v>73</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -1488,10 +1488,10 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1508,34 +1508,34 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="21" t="s">
         <v>88</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2">
+        <v>772105935</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="F27" s="2">
-        <v>778525987</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>96</v>
@@ -1548,10 +1548,10 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="23" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -1568,10 +1568,10 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="20" t="s">
         <v>100</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -1588,10 +1588,10 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="21" t="s">
         <v>100</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -1608,10 +1608,10 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="21" t="s">
         <v>100</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -1628,10 +1628,10 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="23" t="s">
         <v>100</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -1648,10 +1648,10 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="20" t="s">
         <v>113</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -1668,10 +1668,10 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="21" t="s">
         <v>113</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -1688,10 +1688,10 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="21" t="s">
         <v>113</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -1708,10 +1708,10 @@
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="23" t="s">
         <v>113</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -1728,10 +1728,10 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="20" t="s">
         <v>124</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -1748,8 +1748,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A39" s="13"/>
-      <c r="B39" s="11" t="s">
+      <c r="A39" s="19"/>
+      <c r="B39" s="21" t="s">
         <v>124</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -1766,8 +1766,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A40" s="13"/>
-      <c r="B40" s="11" t="s">
+      <c r="A40" s="19"/>
+      <c r="B40" s="21" t="s">
         <v>124</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -1784,8 +1784,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A41" s="14"/>
-      <c r="B41" s="15" t="s">
+      <c r="A41" s="22"/>
+      <c r="B41" s="23" t="s">
         <v>124</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -1802,10 +1802,10 @@
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="20" t="s">
         <v>136</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -1822,10 +1822,10 @@
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="21" t="s">
         <v>136</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -1842,10 +1842,10 @@
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="21" t="s">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -1862,10 +1862,10 @@
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="23" t="s">
         <v>136</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -1885,7 +1885,7 @@
       <c r="A46" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="20" t="s">
         <v>148</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -1903,7 +1903,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="6"/>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -1921,7 +1921,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6"/>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6"/>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C49" s="9" t="s">
@@ -1956,10 +1956,10 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="15" t="s">
         <v>20</v>
       </c>
       <c r="C50" s="8" t="s">
@@ -1976,8 +1976,8 @@
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="17"/>
-      <c r="B51" s="20"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="16"/>
       <c r="C51" s="8" t="s">
         <v>24</v>
       </c>
@@ -1992,8 +1992,8 @@
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="17"/>
-      <c r="B52" s="20"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="16"/>
       <c r="C52" s="8" t="s">
         <v>27</v>
       </c>
@@ -2008,8 +2008,8 @@
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="18"/>
-      <c r="B53" s="21"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="17"/>
       <c r="C53" s="8" t="s">
         <v>30</v>
       </c>
@@ -2026,6 +2026,15 @@
   </sheetData>
   <autoFilter ref="A1:F49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="25">
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A50:A53"/>
@@ -2042,15 +2051,6 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B38:B41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\Dossier LOUMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BEF439B-869A-4A3F-AE9E-B46D81BD02E6}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C35196B-F670-4F5B-B177-60A4FEC348B6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Liste VTO" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste VTO'!$A$1:$F$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste VTO'!$A$1:$F$50</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="162">
   <si>
     <t>DRV</t>
   </si>
@@ -317,6 +317,15 @@
     <t>pvt_mwadk0290</t>
   </si>
   <si>
+    <t>HAMADOU</t>
+  </si>
+  <si>
+    <t>BALDE</t>
+  </si>
+  <si>
+    <t>pvt_mwadk236</t>
+  </si>
+  <si>
     <t>DR SUD</t>
   </si>
   <si>
@@ -324,9 +333,6 @@
   </si>
   <si>
     <t>pvt_mwadk173</t>
-  </si>
-  <si>
-    <t>HAMADOU</t>
   </si>
   <si>
     <t>MBALLO</t>
@@ -703,6 +709,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -726,24 +750,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1025,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="58.85546875" bestFit="1" customWidth="1"/>
@@ -1056,10 +1062,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1076,8 +1082,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A3" s="19"/>
-      <c r="B3" s="21"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1092,8 +1098,8 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="19"/>
-      <c r="B4" s="21"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1114,8 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="19"/>
-      <c r="B5" s="21"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
@@ -1124,10 +1130,10 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="16" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1144,8 +1150,8 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="11"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="8" t="s">
         <v>24</v>
       </c>
@@ -1160,8 +1166,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A8" s="11"/>
-      <c r="B8" s="10"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="8" t="s">
         <v>27</v>
       </c>
@@ -1176,8 +1182,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A9" s="11"/>
-      <c r="B9" s="10"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="8" t="s">
         <v>30</v>
       </c>
@@ -1192,10 +1198,10 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="14" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1212,8 +1218,8 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="19"/>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="14" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1230,8 +1236,8 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="19"/>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="14" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1248,8 +1254,8 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23" t="s">
+      <c r="A13" s="12"/>
+      <c r="B13" s="15" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1266,10 +1272,10 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="13" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1286,8 +1292,8 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="19"/>
-      <c r="B15" s="21" t="s">
+      <c r="A15" s="11"/>
+      <c r="B15" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1304,8 +1310,8 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="19"/>
-      <c r="B16" s="21" t="s">
+      <c r="A16" s="11"/>
+      <c r="B16" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1322,8 +1328,8 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="22"/>
-      <c r="B17" s="23" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="15" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1340,10 +1346,10 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="13" t="s">
         <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1360,8 +1366,8 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="19"/>
-      <c r="B19" s="21" t="s">
+      <c r="A19" s="11"/>
+      <c r="B19" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1378,8 +1384,8 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="19"/>
-      <c r="B20" s="21" t="s">
+      <c r="A20" s="11"/>
+      <c r="B20" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1396,8 +1402,8 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23" t="s">
+      <c r="A21" s="12"/>
+      <c r="B21" s="15" t="s">
         <v>60</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1414,10 +1420,10 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1434,8 +1440,8 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="19"/>
-      <c r="B23" s="21" t="s">
+      <c r="A23" s="11"/>
+      <c r="B23" s="14" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1452,8 +1458,8 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="19"/>
-      <c r="B24" s="21" t="s">
+      <c r="A24" s="11"/>
+      <c r="B24" s="14" t="s">
         <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1470,8 +1476,8 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="22"/>
-      <c r="B25" s="23" t="s">
+      <c r="A25" s="12"/>
+      <c r="B25" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -1488,10 +1494,10 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="13" t="s">
         <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1508,537 +1514,542 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="11"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="2">
-        <v>772105935</v>
-      </c>
+      <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" s="21" t="s">
+      <c r="A28" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="14" t="s">
         <v>88</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>97</v>
       </c>
       <c r="F28" s="2">
-        <v>772104981</v>
+        <v>772105935</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>99</v>
       </c>
       <c r="F29" s="2">
+        <v>772104981</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" s="2">
         <v>772107591</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="18" t="s">
+    <row r="31" spans="1:6">
+      <c r="A31" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="B31" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F30" s="2">
+      <c r="D31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="2">
         <v>777410048</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="2" t="s">
+    <row r="32" spans="1:6">
+      <c r="A32" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="F31" s="2">
-        <v>787656877</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>100</v>
+      <c r="B32" s="14" t="s">
+        <v>102</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2">
+        <v>787656877</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F32" s="2">
+      <c r="D33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="2">
         <v>776019823</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" s="2" t="s">
+    <row r="34" spans="1:6">
+      <c r="A34" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="2">
+      <c r="D34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" s="2">
         <v>782981141</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="18" t="s">
+    <row r="35" spans="1:6">
+      <c r="A35" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="B35" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F35" s="2">
+        <v>788255458</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="F34" s="2">
-        <v>788255458</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F35" s="2">
-        <v>789166919</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>113</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>789151415</v>
+        <v>789166919</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>113</v>
+      <c r="A37" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>115</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2">
+        <v>789151415</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F37" s="2">
+      <c r="D38" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F38" s="2">
         <v>789166998</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A38" s="18" t="s">
+    <row r="39" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A39" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="B39" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F38" s="2">
+      <c r="D39" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F39" s="2">
         <v>781180310</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A39" s="19"/>
-      <c r="B39" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E39" s="2" t="s">
+    <row r="40" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A40" s="11"/>
+      <c r="B40" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F39" s="2">
+      <c r="D40" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" s="2">
         <v>781180552</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A40" s="19"/>
-      <c r="B40" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E40" s="2" t="s">
+    <row r="41" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A41" s="11"/>
+      <c r="B41" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F40" s="2">
-        <v>787080588</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A41" s="22"/>
-      <c r="B41" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F41" s="2">
+        <v>787080588</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A42" s="12"/>
+      <c r="B42" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F42" s="2">
         <v>789150406</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="18" t="s">
+    <row r="43" spans="1:6">
+      <c r="A43" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="B43" s="13" t="s">
         <v>138</v>
-      </c>
-      <c r="F42" s="2">
-        <v>771545210</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>136</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" s="2">
+        <v>771545210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F43" s="2">
+      <c r="D44" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F44" s="2">
         <v>773958904</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E44" s="2" t="s">
+    <row r="45" spans="1:6">
+      <c r="A45" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F44" s="2">
+      <c r="D45" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" s="2">
         <v>776950987</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E45" s="2" t="s">
+    <row r="46" spans="1:6">
+      <c r="A46" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F45" s="2">
+      <c r="D46" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F46" s="2">
         <v>781825193</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="5" t="s">
+    <row r="47" spans="1:6">
+      <c r="A47" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="B47" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F46" s="2">
+      <c r="D47" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F47" s="2">
         <v>786180521</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="6"/>
-      <c r="B47" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F47" s="2">
-        <v>786183517</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6"/>
-      <c r="B48" s="21" t="s">
-        <v>148</v>
+      <c r="B48" s="14" t="s">
+        <v>150</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="F48" s="2">
-        <v>772118585</v>
+        <v>786183517</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6"/>
-      <c r="B49" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C49" s="9" t="s">
+      <c r="B49" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="2">
+        <v>772118585</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="6"/>
+      <c r="B50" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="F49" s="9">
+      <c r="D50" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F50" s="9">
         <v>787389275</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="12" t="s">
+    <row r="51" spans="1:6">
+      <c r="A51" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B51" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C51" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D51" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F51" s="8">
         <v>785249423</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="13"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="8" t="s">
+    <row r="52" spans="1:6">
+      <c r="A52" s="19"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D52" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E52" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F52" s="8">
         <v>784720703</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="13"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="8" t="s">
+    <row r="53" spans="1:6">
+      <c r="A53" s="19"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D53" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E53" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F53" s="8">
         <v>787979910</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="14"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="8" t="s">
+    <row r="54" spans="1:6">
+      <c r="A54" s="20"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D54" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E54" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F54" s="8">
         <v>789514893</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F50" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="25">
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="B51:B54"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A10:A13"/>
@@ -2049,8 +2060,17 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="B22:B25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="B39:B42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29704"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\Dossier LOUMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C35196B-F670-4F5B-B177-60A4FEC348B6}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9899AAE1-988A-4E25-A464-A95A581C4410}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Liste VTO" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste VTO'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste VTO'!$A$1:$F$49</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="160">
   <si>
     <t>DRV</t>
   </si>
@@ -339,12 +339,6 @@
   </si>
   <si>
     <t>pvt_mwadk181</t>
-  </si>
-  <si>
-    <t>MOUHAMADOU KALIDOU</t>
-  </si>
-  <si>
-    <t>pvt_mwadk194</t>
   </si>
   <si>
     <t>PVT ITR (ZONE KAFFRINE)</t>
@@ -709,24 +703,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -750,6 +726,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1031,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="58.85546875" bestFit="1" customWidth="1"/>
@@ -1062,10 +1056,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1082,8 +1076,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A3" s="11"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1098,8 +1092,8 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="11"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1114,8 +1108,8 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="11"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
@@ -1130,10 +1124,10 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1150,8 +1144,8 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="17"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="8" t="s">
         <v>24</v>
       </c>
@@ -1166,8 +1160,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="8" t="s">
         <v>27</v>
       </c>
@@ -1182,8 +1176,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A9" s="17"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="8" t="s">
         <v>30</v>
       </c>
@@ -1198,10 +1192,10 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1218,8 +1212,8 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="11"/>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1236,8 +1230,8 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="11"/>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1254,8 +1248,8 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="12"/>
-      <c r="B13" s="15" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="23" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1272,10 +1266,10 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="20" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1292,8 +1286,8 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="11"/>
-      <c r="B15" s="14" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="21" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1310,8 +1304,8 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="11"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="21" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1328,8 +1322,8 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="12"/>
-      <c r="B17" s="15" t="s">
+      <c r="A17" s="22"/>
+      <c r="B17" s="23" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1346,10 +1340,10 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="20" t="s">
         <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1366,8 +1360,8 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="11"/>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="19"/>
+      <c r="B19" s="21" t="s">
         <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1384,8 +1378,8 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="11"/>
-      <c r="B20" s="14" t="s">
+      <c r="A20" s="19"/>
+      <c r="B20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1402,8 +1396,8 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="12"/>
-      <c r="B21" s="15" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="23" t="s">
         <v>60</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1420,10 +1414,10 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="20" t="s">
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1440,8 +1434,8 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="11"/>
-      <c r="B23" s="14" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1458,8 +1452,8 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="11"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="19"/>
+      <c r="B24" s="21" t="s">
         <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1476,8 +1470,8 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="12"/>
-      <c r="B25" s="15" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="23" t="s">
         <v>73</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -1494,10 +1488,10 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1514,8 +1508,8 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="11"/>
-      <c r="B27" s="14"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="21"/>
       <c r="C27" s="2" t="s">
         <v>92</v>
       </c>
@@ -1525,13 +1519,15 @@
       <c r="E27" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="2"/>
+      <c r="F27" s="2">
+        <v>778525987</v>
+      </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="21" t="s">
         <v>88</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -1548,10 +1544,10 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="21" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -1568,488 +1564,477 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>88</v>
+      <c r="A30" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="2">
+        <v>777410048</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F30" s="2">
-        <v>772107591</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>102</v>
-      </c>
       <c r="C31" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="2">
+        <v>787656877</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F31" s="2">
-        <v>777410048</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>102</v>
+      <c r="B32" s="21" t="s">
+        <v>100</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F32" s="2">
-        <v>787656877</v>
+        <v>776019823</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>102</v>
+      <c r="A33" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>100</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F33" s="2">
-        <v>776019823</v>
+        <v>782981141</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>102</v>
+      <c r="A34" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>113</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F34" s="2">
+        <v>788255458</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F34" s="2">
-        <v>782981141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>115</v>
-      </c>
       <c r="C35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" s="2">
+        <v>789166919</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F35" s="2">
-        <v>788255458</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>115</v>
+      <c r="B36" s="21" t="s">
+        <v>113</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>789166919</v>
+        <v>789151415</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>115</v>
+      <c r="A37" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>113</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F37" s="2">
-        <v>789151415</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>115</v>
+        <v>789166998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A38" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>124</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" s="2">
+        <v>781180310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="14.45" customHeight="1">
+      <c r="A39" s="19"/>
+      <c r="B39" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F38" s="2">
-        <v>789166998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A39" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>126</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F39" s="2">
-        <v>781180310</v>
+        <v>781180552</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A40" s="11"/>
-      <c r="B40" s="14" t="s">
-        <v>126</v>
+      <c r="A40" s="19"/>
+      <c r="B40" s="21" t="s">
+        <v>124</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F40" s="2">
-        <v>781180552</v>
+        <v>787080588</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A41" s="11"/>
-      <c r="B41" s="14" t="s">
-        <v>126</v>
+      <c r="A41" s="22"/>
+      <c r="B41" s="23" t="s">
+        <v>124</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F41" s="2">
-        <v>787080588</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A42" s="12"/>
-      <c r="B42" s="15" t="s">
-        <v>126</v>
+        <v>789150406</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>136</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="2">
+        <v>771545210</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="21" t="s">
         <v>136</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="2">
-        <v>789150406</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F43" s="2">
-        <v>771545210</v>
+        <v>773958904</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="14" t="s">
-        <v>138</v>
+      <c r="B44" s="21" t="s">
+        <v>136</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>773958904</v>
+        <v>776950987</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="14" t="s">
-        <v>138</v>
+      <c r="B45" s="23" t="s">
+        <v>136</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F45" s="2">
-        <v>776950987</v>
+        <v>781825193</v>
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>138</v>
+      <c r="A46" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>148</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F46" s="2">
+        <v>786180521</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="6"/>
+      <c r="B47" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F46" s="2">
-        <v>781825193</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>150</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F47" s="2">
-        <v>786180521</v>
+        <v>786183517</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6"/>
-      <c r="B48" s="14" t="s">
-        <v>150</v>
+      <c r="B48" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F48" s="2">
-        <v>786183517</v>
+        <v>772118585</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6"/>
-      <c r="B49" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="B49" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F49" s="2">
-        <v>772118585</v>
+      <c r="F49" s="9">
+        <v>787389275</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="6"/>
-      <c r="B50" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F50" s="9">
-        <v>787389275</v>
+      <c r="A50" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" s="8">
+        <v>785249423</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>20</v>
-      </c>
+      <c r="A51" s="13"/>
+      <c r="B51" s="16"/>
       <c r="C51" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F51" s="8">
-        <v>785249423</v>
+        <v>784720703</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="19"/>
-      <c r="B52" s="22"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="16"/>
       <c r="C52" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F52" s="8">
-        <v>784720703</v>
+        <v>787979910</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="19"/>
-      <c r="B53" s="22"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="17"/>
       <c r="C53" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F53" s="8">
-        <v>787979910</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="20"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F54" s="8">
         <v>789514893</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F50" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="25">
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="B50:B53"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A10:A13"/>
@@ -2060,17 +2045,8 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="B22:B25"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="B47:B50"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\Dossier LOUMA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonatelworkplace-my.sharepoint.com/personal/fall7435_orange-sonatel_com/Documents/Bureau/DOSSIER LOUMAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="11_62E75E214BEF08387827ABE3F4F2BDEBE23AB00D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9899AAE1-988A-4E25-A464-A95A581C4410}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74E245E8-0796-4B53-BD4A-38ACBE93A1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste VTO" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="167">
   <si>
     <t>DRV</t>
   </si>
@@ -158,9 +158,6 @@
     <t>LO</t>
   </si>
   <si>
-    <t>pvt_smmc2928</t>
-  </si>
-  <si>
     <t>GAMOU</t>
   </si>
   <si>
@@ -392,27 +389,6 @@
     <t>NORD</t>
   </si>
   <si>
-    <t>ALLA  SOW</t>
-  </si>
-  <si>
-    <t>Pvt_tdc590043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABIBOU  </t>
-  </si>
-  <si>
-    <t>Pvt_tdc590120</t>
-  </si>
-  <si>
-    <t>BILALY</t>
-  </si>
-  <si>
-    <t>BASSOUM</t>
-  </si>
-  <si>
-    <t>Pvt_tdc590016</t>
-  </si>
-  <si>
     <t>PVT FOFANA SORIKE KEDOUGOU (RAVT ZONE KEDOUGOU)</t>
   </si>
   <si>
@@ -488,44 +464,89 @@
     <t>PVT TOUBA BOGO COMMUNICATION (ZONE MBOUR)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gnima </t>
-  </si>
-  <si>
-    <t>Diatta</t>
-  </si>
-  <si>
     <t>pvt_tbogo1367</t>
   </si>
   <si>
-    <t>Rose Mendy</t>
-  </si>
-  <si>
-    <t>Mendy</t>
-  </si>
-  <si>
     <t>pvt_tbogo1124</t>
   </si>
   <si>
-    <t xml:space="preserve">Pauline coumba </t>
-  </si>
-  <si>
-    <t>Faye</t>
-  </si>
-  <si>
     <t>pvt_tbogo1534</t>
   </si>
   <si>
-    <t>Fall</t>
-  </si>
-  <si>
-    <t>pvt_tbogo1719</t>
+    <t>pvt_smmc3467</t>
+  </si>
+  <si>
+    <t>MATY</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590014</t>
+  </si>
+  <si>
+    <t>MMAME KHASS</t>
+  </si>
+  <si>
+    <t>SYLLA</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590021</t>
+  </si>
+  <si>
+    <t>BASSIROU</t>
+  </si>
+  <si>
+    <t>DIAW</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590313</t>
+  </si>
+  <si>
+    <t>ASSANE</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1864</t>
+  </si>
+  <si>
+    <t>LOUISE MAME LISSA</t>
+  </si>
+  <si>
+    <t>Pvt_ibsen0551</t>
+  </si>
+  <si>
+    <t>MAREME</t>
+  </si>
+  <si>
+    <t>TOURE</t>
+  </si>
+  <si>
+    <t>Pvt_ibsen0550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSE </t>
+  </si>
+  <si>
+    <t>MENDY</t>
+  </si>
+  <si>
+    <t>FAYE</t>
+  </si>
+  <si>
+    <t>PAULINE COUMBA</t>
+  </si>
+  <si>
+    <t>GNIMA</t>
+  </si>
+  <si>
+    <t>DIATTA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -563,7 +584,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,7 +714,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -703,6 +723,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -727,24 +765,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1026,16 +1047,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1055,11 +1076,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1075,9 +1096,9 @@
         <v>782989910</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A3" s="19"/>
-      <c r="B3" s="21"/>
+    <row r="3" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1091,9 +1112,9 @@
         <v>787095594</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="19"/>
-      <c r="B4" s="21"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="10"/>
+      <c r="B4" s="13"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1107,95 +1128,95 @@
         <v>781180981</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="19"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="9" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="10"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>787095584</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>785249423</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="11"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="8" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="16"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>784720703</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A8" s="11"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="8" t="s">
+    <row r="8" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>787979910</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A9" s="11"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="8" t="s">
+    <row r="9" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="16"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>789514893</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="13" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1208,12 +1229,12 @@
         <v>36</v>
       </c>
       <c r="F10" s="2">
-        <v>786241266</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="19"/>
-      <c r="B11" s="21" t="s">
+        <v>781990323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="10"/>
+      <c r="B11" s="13" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1223,814 +1244,805 @@
         <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="2">
+        <v>710019414</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="10"/>
+      <c r="B12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="2">
-        <v>789160174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="19"/>
-      <c r="B12" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F12" s="2">
         <v>786241255</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="14" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="2">
+        <v>789160171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="2">
-        <v>775812208</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="18" t="s">
+      <c r="B14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="C14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="F14" s="2">
         <v>789166714</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="19"/>
-      <c r="B15" s="21" t="s">
-        <v>46</v>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="10"/>
+      <c r="B15" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="3" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="10"/>
+      <c r="B16" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="19"/>
-      <c r="B16" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F16" s="2">
         <v>789166702</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="22"/>
-      <c r="B17" s="23" t="s">
-        <v>46</v>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="11"/>
+      <c r="B17" s="14" t="s">
+        <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="F17" s="2">
         <v>787655205</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="18" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="C18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="19"/>
-      <c r="B19" s="21" t="s">
-        <v>60</v>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="10"/>
+      <c r="B19" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F19" s="2">
         <v>787080726</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="19"/>
-      <c r="B20" s="21" t="s">
-        <v>60</v>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="10"/>
+      <c r="B20" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="F20" s="2">
         <v>787081068</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23" t="s">
-        <v>60</v>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="11"/>
+      <c r="B21" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="F21" s="2">
         <v>781590999</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="18" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="C22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="3" t="s">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="10"/>
+      <c r="B23" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="19"/>
-      <c r="B23" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="3" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="10"/>
+      <c r="B24" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="19"/>
-      <c r="B24" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="3" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="11"/>
+      <c r="B25" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="22"/>
-      <c r="B25" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="23">
+        <v>789167632</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="4">
-        <v>789167632</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="18" t="s">
+      <c r="B26" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="C26" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="F26" s="2">
         <v>775810336</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="19"/>
-      <c r="B27" s="21"/>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="10"/>
+      <c r="B27" s="13"/>
       <c r="C27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="F27" s="2">
         <v>778525987</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="19" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F28" s="2">
         <v>772105935</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>88</v>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="F29" s="2">
         <v>772104981</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="20" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="F30" s="2">
         <v>777410048</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="19" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="F31" s="2">
         <v>787656877</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>100</v>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="F32" s="2">
         <v>776019823</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>100</v>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="F33" s="2">
         <v>782981141</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="20" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="F34" s="2">
         <v>788255458</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="19" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F35" s="2">
+        <v>789157751</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" s="2">
+        <v>789166902</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F37" s="2">
+        <v>710015134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F35" s="2">
-        <v>789166919</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F36" s="2">
-        <v>789151415</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F37" s="2">
-        <v>789166998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A38" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="F38" s="2">
         <v>781180310</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A39" s="19"/>
-      <c r="B39" s="21" t="s">
-        <v>124</v>
+    <row r="39" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="10"/>
+      <c r="B39" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F39" s="2">
         <v>781180552</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A40" s="19"/>
-      <c r="B40" s="21" t="s">
+    <row r="40" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="10"/>
+      <c r="B40" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="E40" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F40" s="2">
         <v>787080588</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A41" s="22"/>
-      <c r="B41" s="23" t="s">
-        <v>124</v>
+    <row r="41" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="11"/>
+      <c r="B41" s="14" t="s">
+        <v>116</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F41" s="2">
         <v>789150406</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>136</v>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F42" s="2">
         <v>771545210</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>136</v>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F43" s="2">
         <v>773958904</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B44" s="21" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F44" s="2">
         <v>776950987</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>136</v>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F45" s="2">
         <v>781825193</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>148</v>
+      <c r="B46" s="12" t="s">
+        <v>140</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F46" s="2">
         <v>786180521</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="6"/>
-      <c r="B47" s="21" t="s">
-        <v>148</v>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="5"/>
+      <c r="B47" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F47" s="2">
         <v>786183517</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="6"/>
-      <c r="B48" s="21" t="s">
-        <v>148</v>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="5"/>
+      <c r="B48" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="F48" s="2">
         <v>772118585</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="6"/>
-      <c r="B49" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49" s="9" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="5"/>
+      <c r="B49" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F49" s="8">
+        <v>789157530</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F50" s="7">
+        <v>789217447</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="18"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="D51" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F49" s="9">
-        <v>787389275</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F50" s="8">
-        <v>785249423</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="13"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F51" s="8">
-        <v>784720703</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="13"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="8" t="s">
+      <c r="E51" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F51" s="7">
+        <v>783059147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="18"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="7">
         <v>787979910</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="14"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="8" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="19"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="7">
         <v>789514893</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="25">
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B38:B41"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A50:A53"/>
@@ -2047,6 +2059,15 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:B41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonatelworkplace-my.sharepoint.com/personal/fall7435_orange-sonatel_com/Documents/Bureau/DOSSIER LOUMAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74E245E8-0796-4B53-BD4A-38ACBE93A1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{74E245E8-0796-4B53-BD4A-38ACBE93A1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A3E7552-24B7-42DC-B18D-941C2BD1E935}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="161">
   <si>
     <t>DRV</t>
   </si>
@@ -104,24 +104,9 @@
     <t>IBRAHIMA SENE(SADI ZPPG)</t>
   </si>
   <si>
-    <t xml:space="preserve">KHADIM </t>
-  </si>
-  <si>
-    <t>NIANG</t>
-  </si>
-  <si>
-    <t>Pvt_ibsen0464</t>
-  </si>
-  <si>
-    <t>CHEIKH</t>
-  </si>
-  <si>
     <t>DIOP</t>
   </si>
   <si>
-    <t>Pvt_ibsen0440</t>
-  </si>
-  <si>
     <t xml:space="preserve">BOUSSO </t>
   </si>
   <si>
@@ -239,9 +224,6 @@
     <t>pvt_mbpling0268</t>
   </si>
   <si>
-    <t xml:space="preserve">Fallou </t>
-  </si>
-  <si>
     <t>pvt_mbpling0274</t>
   </si>
   <si>
@@ -404,9 +386,6 @@
     <t xml:space="preserve">HARIDIATOU </t>
   </si>
   <si>
-    <t xml:space="preserve"> DIALLO</t>
-  </si>
-  <si>
     <t>pvt_sfof097</t>
   </si>
   <si>
@@ -540,6 +519,9 @@
   </si>
   <si>
     <t>DIATTA</t>
+  </si>
+  <si>
+    <t>FALLOU</t>
   </si>
 </sst>
 </file>
@@ -589,7 +571,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -665,39 +647,52 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -705,7 +700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -714,22 +709,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -738,34 +731,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1046,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="58.81640625" bestFit="1" customWidth="1"/>
@@ -1077,7 +1067,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -1097,7 +1087,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="13"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
@@ -1113,7 +1103,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="10"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="13"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
@@ -1129,924 +1119,863 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="10"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="13"/>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="6">
         <v>787095584</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" s="5">
+        <v>789217447</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="5">
+        <v>783059147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="D8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="7">
-        <v>785249423</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="7" t="s">
+      <c r="E8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="F8" s="5">
+        <v>787979010</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="7">
-        <v>784720703</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="7" t="s">
+      <c r="E9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="F9" s="5">
+        <v>789514893</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="B10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="7">
-        <v>787979910</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="16"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="7" t="s">
+      <c r="C10" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="7">
-        <v>789514893</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F10" s="2">
         <v>781990323</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="10"/>
+      <c r="A11" s="11"/>
       <c r="B11" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F11" s="2">
         <v>710019414</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="10"/>
+      <c r="A12" s="11"/>
       <c r="B12" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2">
         <v>786241255</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="14" t="s">
-        <v>34</v>
+      <c r="A13" s="14"/>
+      <c r="B13" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F13" s="2">
         <v>789160171</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>44</v>
+      <c r="A14" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F14" s="2">
         <v>789166714</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="10"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="10"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="13" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F16" s="2">
         <v>789166702</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
-      <c r="B17" s="14" t="s">
-        <v>45</v>
+      <c r="A17" s="14"/>
+      <c r="B17" s="15" t="s">
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2">
         <v>787655205</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="12" t="s">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="11"/>
+      <c r="B19" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="10"/>
-      <c r="B19" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F19" s="2">
         <v>787080726</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="10"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F20" s="2">
         <v>787081068</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="11"/>
-      <c r="B21" s="14" t="s">
-        <v>59</v>
+      <c r="A21" s="14"/>
+      <c r="B21" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2">
         <v>781590999</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="11"/>
+      <c r="B23" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="F23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="2" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="11"/>
+      <c r="B24" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="10"/>
-      <c r="B23" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="2" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="14"/>
+      <c r="B25" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="10"/>
-      <c r="B24" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="F25" s="7">
+        <v>789167632</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="B26" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="11"/>
-      <c r="B25" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="23">
-        <v>789167632</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="F26" s="2">
         <v>775810336</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="10"/>
+      <c r="A27" s="11"/>
       <c r="B27" s="13"/>
       <c r="C27" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F27" s="2">
         <v>778525987</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="10" t="s">
-        <v>94</v>
+      <c r="A28" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F28" s="2">
         <v>772105935</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
-        <v>94</v>
+      <c r="A29" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F29" s="2">
         <v>772104981</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
-        <v>44</v>
+      <c r="A30" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F30" s="2">
         <v>777410048</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
-        <v>103</v>
+      <c r="A31" s="11" t="s">
+        <v>97</v>
       </c>
       <c r="B31" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="F31" s="2">
         <v>787656877</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="10" t="s">
-        <v>103</v>
+      <c r="A32" s="11" t="s">
+        <v>97</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F32" s="2">
         <v>776019823</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F33" s="2">
         <v>782981141</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
-        <v>58</v>
+      <c r="A34" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F34" s="2">
         <v>788255458</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
-        <v>115</v>
+      <c r="A35" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F35" s="2">
         <v>789157751</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="10" t="s">
-        <v>115</v>
+      <c r="A36" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F36" s="2">
         <v>789166902</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>112</v>
+      <c r="A37" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F37" s="2">
         <v>710015134</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="9" t="s">
-        <v>71</v>
+      <c r="A38" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F38" s="2">
         <v>781180310</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="10"/>
+      <c r="A39" s="11"/>
       <c r="B39" s="13" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F39" s="2">
         <v>781180552</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="10"/>
+      <c r="A40" s="11"/>
       <c r="B40" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F40" s="2">
         <v>787080588</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="11"/>
-      <c r="B41" s="14" t="s">
-        <v>116</v>
+      <c r="A41" s="14"/>
+      <c r="B41" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F41" s="2">
         <v>789150406</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
-        <v>86</v>
+      <c r="A42" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F42" s="2">
         <v>771545210</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="10" t="s">
-        <v>94</v>
+      <c r="A43" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F43" s="2">
         <v>773958904</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="10" t="s">
-        <v>94</v>
+      <c r="A44" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="B44" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="E44" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="F44" s="2">
         <v>776950987</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>128</v>
+        <v>88</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F45" s="2">
         <v>781825193</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>165</v>
+      <c r="A46" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>158</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F46" s="2">
-        <v>786180521</v>
+        <v>786182105</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="5"/>
-      <c r="B47" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>161</v>
+      <c r="A47" s="21"/>
+      <c r="B47" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F47" s="2">
         <v>786183517</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="5"/>
-      <c r="B48" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>164</v>
+      <c r="A48" s="21"/>
+      <c r="B48" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>157</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F48" s="2">
         <v>772118585</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="5"/>
-      <c r="B49" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="F49" s="8">
+    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="22"/>
+      <c r="B49" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F49" s="2">
         <v>789157530</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F50" s="7">
-        <v>789217447</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="18"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F51" s="7">
-        <v>783059147</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="18"/>
-      <c r="B52" s="21"/>
-      <c r="C52" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F52" s="7">
-        <v>787979910</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="19"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F53" s="7">
-        <v>789514893</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="25">
+  <mergeCells count="24">
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A46:A49"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="B50:B53"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A10:A13"/>
@@ -2059,15 +1988,6 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B38:B41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projets\ISDC\dv\louma-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonatelworkplace-my.sharepoint.com/personal/fall7435_orange-sonatel_com/Documents/Bureau/DOSSIER LOUMAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD7CCFB-6BBB-44B3-BA40-146C481F8992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{40ED9D43-4F44-4B93-A6D3-4D729016E810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3105BA3-75DC-4535-A77A-CC3663EA9A8A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="161">
   <si>
     <t>DRV</t>
   </si>
@@ -305,12 +305,6 @@
     <t>DR EST</t>
   </si>
   <si>
-    <t>PAPE ABDOULAYE</t>
-  </si>
-  <si>
-    <t>pvt_itrkaf0585</t>
-  </si>
-  <si>
     <t>ROKY</t>
   </si>
   <si>
@@ -347,15 +341,6 @@
     <t>PVT FOFANA SORIKE KEDOUGOU (RAVT ZONE KEDOUGOU)</t>
   </si>
   <si>
-    <t xml:space="preserve">VIEUX </t>
-  </si>
-  <si>
-    <t>DANSOKHO</t>
-  </si>
-  <si>
-    <t>pvt_sfof126</t>
-  </si>
-  <si>
     <t xml:space="preserve">HARIDIATOU </t>
   </si>
   <si>
@@ -525,13 +510,25 @@
   </si>
   <si>
     <t>pvt_mwadk0627</t>
+  </si>
+  <si>
+    <t>GORA</t>
+  </si>
+  <si>
+    <t>SECK</t>
+  </si>
+  <si>
+    <t>pvt_itrkaf0701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pvt_sfof0294 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -565,6 +562,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -679,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -701,11 +704,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -716,14 +720,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -740,6 +748,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1036,10 +1048,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1056,8 +1068,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16"/>
-      <c r="B3" s="19"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1072,8 +1084,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="16"/>
-      <c r="B4" s="19"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1088,8 +1100,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
-      <c r="B5" s="20"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="19"/>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1104,10 +1116,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1124,8 +1136,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="19" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -1135,15 +1147,15 @@
         <v>25</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F7" s="4">
         <v>710019414</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
-      <c r="B8" s="19" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1160,8 +1172,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="17"/>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1178,10 +1190,10 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="14" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1198,8 +1210,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="19" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="15" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1216,8 +1228,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="19" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="15" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1234,8 +1246,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="17"/>
-      <c r="B13" s="20" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1252,10 +1264,10 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1272,8 +1284,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="19" t="s">
+      <c r="A15" s="17"/>
+      <c r="B15" s="15" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1290,12 +1302,12 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="17"/>
+      <c r="B16" s="15" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>27</v>
@@ -1308,8 +1320,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="17"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1326,10 +1338,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="14" t="s">
         <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1346,8 +1358,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="16"/>
-      <c r="B19" s="19" t="s">
+      <c r="A19" s="17"/>
+      <c r="B19" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1364,8 +1376,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="16"/>
-      <c r="B20" s="19" t="s">
+      <c r="A20" s="17"/>
+      <c r="B20" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1382,8 +1394,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="17"/>
-      <c r="B21" s="20" t="s">
+      <c r="A21" s="18"/>
+      <c r="B21" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1400,10 +1412,10 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="14" t="s">
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1420,10 +1432,10 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1440,10 +1452,10 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1460,30 +1472,30 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="19" t="s">
         <v>73</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F25" s="12">
         <v>789168927</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="14" t="s">
         <v>83</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1500,294 +1512,294 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" s="13">
+        <v>787084130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="2">
-        <v>787656877</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F28" s="2">
         <v>776019823</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="19" t="s">
         <v>83</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F29" s="2">
         <v>782981141</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>96</v>
+      <c r="B30" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F30" s="2">
         <v>788255458</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>96</v>
+      <c r="A31" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>94</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F31" s="4">
         <v>789157751</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>96</v>
+      <c r="A32" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>94</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F32" s="4">
         <v>789166902</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>96</v>
+      <c r="A33" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>94</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F33" s="4">
         <v>710015134</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="15" t="s">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.4">
+      <c r="A34" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" s="23">
+        <v>789150581</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="17"/>
+      <c r="B35" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F34" s="2">
-        <v>781180310</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="16"/>
-      <c r="B35" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="F35" s="2">
         <v>781180552</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="16"/>
-      <c r="B36" s="19" t="s">
-        <v>101</v>
+      <c r="A36" s="17"/>
+      <c r="B36" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F36" s="2">
         <v>787080588</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="17"/>
-      <c r="B37" s="20" t="s">
-        <v>101</v>
+      <c r="A37" s="18"/>
+      <c r="B37" s="19" t="s">
+        <v>99</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F37" s="2">
         <v>789150406</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>113</v>
+      <c r="B38" s="14" t="s">
+        <v>108</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F38" s="2">
         <v>771545210</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="F39" s="2">
         <v>773958904</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>113</v>
+      <c r="B40" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F40" s="2">
         <v>776950987</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>113</v>
+      <c r="B41" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F41" s="2">
         <v>781825193</v>
@@ -1797,17 +1809,17 @@
       <c r="A42" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>125</v>
+      <c r="B42" s="14" t="s">
+        <v>120</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F42" s="2">
         <v>786180521</v>
@@ -1815,17 +1827,17 @@
     </row>
     <row r="43" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6"/>
-      <c r="B43" s="19" t="s">
-        <v>125</v>
+      <c r="B43" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F43" s="2">
         <v>786183517</v>
@@ -1833,17 +1845,17 @@
     </row>
     <row r="44" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6"/>
-      <c r="B44" s="19" t="s">
-        <v>125</v>
+      <c r="B44" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F44" s="2">
         <v>772118585</v>
@@ -1851,99 +1863,93 @@
     </row>
     <row r="45" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6"/>
-      <c r="B45" s="19" t="s">
-        <v>125</v>
+      <c r="B45" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F45" s="9">
         <v>789157530</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>129</v>
+      <c r="B46" s="21" t="s">
+        <v>124</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F46" s="10">
         <v>789217447</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="21"/>
       <c r="C47" s="10" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F47" s="10">
         <v>783059147</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="21"/>
       <c r="C48" s="7" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F48" s="7">
         <v>787979910</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="21"/>
       <c r="C49" s="7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F49" s="7">
         <v>789514893</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="23">
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="A2:A5"/>
@@ -1960,6 +1966,13 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonatelworkplace-my.sharepoint.com/personal/fall7435_orange-sonatel_com/Documents/Bureau/DOSSIER LOUMAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seye028962\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{40ED9D43-4F44-4B93-A6D3-4D729016E810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3105BA3-75DC-4535-A77A-CC3663EA9A8A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23BEACC6-720B-4E64-8247-A5A474F6EB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-2595" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste VTO" sheetId="1" r:id="rId1"/>
@@ -38,8 +38,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Ndeye Gnagna FALL [SNT DV/DOC/DVTC/DVTF]</author>
+  </authors>
+  <commentList>
+    <comment ref="F33" authorId="0" shapeId="0" xr:uid="{636FDE32-73F1-4010-ACD5-A498C581F56C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ndeye Gnagna FALL [SNT DV/DOC/DVTC/DVTF]:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="162">
   <si>
     <t>DRV</t>
   </si>
@@ -326,12 +360,6 @@
     <t>PVT Thomas Djibril Ciss (RAVT KEBEMER)</t>
   </si>
   <si>
-    <t xml:space="preserve">ABDOU LAHAD </t>
-  </si>
-  <si>
-    <t>Pvt_tdc590013</t>
-  </si>
-  <si>
     <t>NORD</t>
   </si>
   <si>
@@ -437,15 +465,9 @@
     <t>pvt_smmc3467</t>
   </si>
   <si>
-    <t>Pvt_tdc590313</t>
-  </si>
-  <si>
     <t>DIAW</t>
   </si>
   <si>
-    <t>BASSIROU</t>
-  </si>
-  <si>
     <t>MATY</t>
   </si>
   <si>
@@ -521,14 +543,29 @@
     <t>pvt_itrkaf0701</t>
   </si>
   <si>
-    <t xml:space="preserve">pvt_sfof0294 </t>
+    <t>ABDOURAHMANE</t>
+  </si>
+  <si>
+    <t>pvt_tdc590105</t>
+  </si>
+  <si>
+    <t>pvt_tdc590316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIERNO AMADOU DIAN </t>
+  </si>
+  <si>
+    <t>pvt_sfof0229</t>
+  </si>
+  <si>
+    <t>WANE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,7 +591,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -564,10 +601,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -590,7 +665,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -678,19 +753,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -705,11 +790,34 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -720,18 +828,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -748,10 +852,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1016,7 +1116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1024,7 +1124,7 @@
     <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1043,15 +1143,15 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="35" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1063,13 +1163,13 @@
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="21">
         <v>782989910</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17"/>
-      <c r="B3" s="15"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="36"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1079,13 +1179,13 @@
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="21">
         <v>787095594</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="17"/>
-      <c r="B4" s="15"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1095,13 +1195,13 @@
       <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="21">
         <v>781180981</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1111,15 +1211,15 @@
       <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="21">
         <v>787095584</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="35" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1131,31 +1231,31 @@
       <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="22">
         <v>781990323</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="17"/>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="33"/>
+      <c r="B7" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="E7" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="22">
         <v>710019414</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="17"/>
-      <c r="B8" s="15" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="36" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1167,13 +1267,13 @@
       <c r="E8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="21">
         <v>786241255</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="37" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1185,15 +1285,15 @@
       <c r="E9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="22">
         <v>789160171</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="35" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1205,13 +1305,13 @@
       <c r="E10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="21">
         <v>789166714</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="17"/>
-      <c r="B11" s="15" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="36" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1223,13 +1323,13 @@
       <c r="E11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="23" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="17"/>
-      <c r="B12" s="15" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="36" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1241,13 +1341,13 @@
       <c r="E12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="21">
         <v>789166702</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="37" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1259,15 +1359,15 @@
       <c r="E13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="21">
         <v>787655205</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="35" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1279,13 +1379,13 @@
       <c r="E14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="23" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="17"/>
-      <c r="B15" s="15" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="36" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1297,17 +1397,17 @@
       <c r="E15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="21">
         <v>787080726</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="17"/>
-      <c r="B16" s="15" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="36" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>27</v>
@@ -1315,13 +1415,13 @@
       <c r="E16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="21">
         <v>787081068</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="37" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1333,15 +1433,15 @@
       <c r="E17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="21">
         <v>781590999</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="35" t="s">
         <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1353,13 +1453,13 @@
       <c r="E18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="23" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="17"/>
-      <c r="B19" s="15" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="36" t="s">
         <v>58</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1371,13 +1471,13 @@
       <c r="E19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="23" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="17"/>
-      <c r="B20" s="15" t="s">
+      <c r="A20" s="33"/>
+      <c r="B20" s="36" t="s">
         <v>58</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1389,13 +1489,13 @@
       <c r="E20" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="23" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19" t="s">
+      <c r="A21" s="34"/>
+      <c r="B21" s="37" t="s">
         <v>58</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1407,15 +1507,15 @@
       <c r="E21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="24">
         <v>789167632</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="35" t="s">
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1427,15 +1527,15 @@
       <c r="E22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="21">
         <v>775810336</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="36" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1447,15 +1547,15 @@
       <c r="E23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="21">
         <v>778525987</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="36" t="s">
         <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1467,35 +1567,35 @@
       <c r="E24" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="21">
         <v>772104981</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="37" t="s">
         <v>73</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F25" s="12">
+      <c r="E25" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="11">
         <v>789168927</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="35" t="s">
         <v>83</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1507,35 +1607,35 @@
       <c r="E26" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="21">
         <v>777410048</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="F27" s="13">
+      <c r="C27" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27" s="12">
         <v>787084130</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="36" t="s">
         <v>83</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -1547,15 +1647,15 @@
       <c r="E28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="21">
         <v>776019823</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="37" t="s">
         <v>83</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -1567,389 +1667,396 @@
       <c r="E29" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="21">
         <v>782981141</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F30" s="25">
+        <v>710021900</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" s="2">
-        <v>788255458</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="17" t="s">
+      <c r="B31" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" s="22">
+        <v>789157751</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="22">
+        <v>789166902</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" s="21">
+        <v>789166982</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.4">
+      <c r="A34" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F31" s="4">
-        <v>789157751</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="17" t="s">
+      <c r="C34" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" s="11">
+        <v>710017946</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="33"/>
+      <c r="B35" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F32" s="4">
-        <v>789166902</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="18" t="s">
+      <c r="C35" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" s="21">
+        <v>781180552</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="33"/>
+      <c r="B36" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F33" s="4">
-        <v>710015134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A34" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="F34" s="23">
-        <v>789150581</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="17"/>
-      <c r="B35" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F35" s="2">
-        <v>781180552</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="17"/>
-      <c r="B36" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="F36" s="21">
+        <v>787080588</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="34"/>
+      <c r="B37" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="D37" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F36" s="2">
-        <v>787080588</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="18"/>
-      <c r="B37" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="F37" s="21">
+        <v>789150406</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="F37" s="2">
-        <v>789150406</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="21">
+        <v>771545210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F38" s="2">
-        <v>771545210</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="17" t="s">
+      <c r="E39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="21">
+        <v>773958904</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="B40" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F39" s="2">
-        <v>773958904</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="17" t="s">
+      <c r="E40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F40" s="21">
+        <v>776950987</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="B41" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F40" s="2">
-        <v>776950987</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="F41" s="21">
+        <v>781825193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F41" s="2">
-        <v>781825193</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B42" s="14" t="s">
+      <c r="F42" s="21">
+        <v>786180521</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="5"/>
+      <c r="B43" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="F43" s="21">
+        <v>786183517</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="5"/>
+      <c r="B44" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="21">
+        <v>772118585</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="5"/>
+      <c r="B45" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F45" s="26">
+        <v>789157530</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F46" s="27">
+        <v>789217447</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D47" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F42" s="2">
-        <v>786180521</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="6"/>
-      <c r="B43" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F43" s="2">
-        <v>786183517</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="6"/>
-      <c r="B44" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E44" s="2" t="s">
+      <c r="E47" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F47" s="27">
+        <v>783059147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="30"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F44" s="2">
-        <v>772118585</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="6"/>
-      <c r="B45" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F45" s="9">
-        <v>789157530</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="21" t="s">
+      <c r="D48" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F46" s="10">
-        <v>789217447</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="20"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="F47" s="10">
-        <v>783059147</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="20"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="7" t="s">
+      <c r="E48" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="F48" s="28">
+        <v>787979910</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="D49" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F48" s="7">
-        <v>787979910</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="20"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="7" t="s">
+      <c r="E49" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D49" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="F49" s="7">
+      <c r="F49" s="28">
         <v>789514893</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="23">
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="A2:A5"/>
@@ -1966,14 +2073,8 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seye028962\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonatelworkplace-my.sharepoint.com/personal/fall7435_orange-sonatel_com/Documents/Bureau/DOSSIER LOUMAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23BEACC6-720B-4E64-8247-A5A474F6EB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{40ED9D43-4F44-4B93-A6D3-4D729016E810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D922CF88-E92E-4202-957E-3798E5CC74D3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2595" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste VTO" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="161">
   <si>
     <t>DRV</t>
   </si>
@@ -201,15 +201,6 @@
     <t>pvt_dfallf0418</t>
   </si>
   <si>
-    <t>MOUSTAPHA</t>
-  </si>
-  <si>
-    <t>DIAKHATE</t>
-  </si>
-  <si>
-    <t>pvt_dfallf0183</t>
-  </si>
-  <si>
     <t>DRN</t>
   </si>
   <si>
@@ -559,6 +550,12 @@
   </si>
   <si>
     <t>WANE</t>
+  </si>
+  <si>
+    <t>PAPA MOMAR</t>
+  </si>
+  <si>
+    <t>pvt_dfallf0510</t>
   </si>
 </sst>
 </file>
@@ -770,7 +767,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -802,14 +799,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -852,6 +844,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1124,7 +1120,7 @@
     <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" style="25" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1148,10 +1144,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1163,13 +1159,13 @@
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="2">
         <v>782989910</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33"/>
-      <c r="B3" s="36"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1179,13 +1175,13 @@
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="2">
         <v>787095594</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="33"/>
-      <c r="B4" s="36"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1195,13 +1191,13 @@
       <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="2">
         <v>781180981</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="34"/>
-      <c r="B5" s="37"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1211,15 +1207,15 @@
       <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="2">
         <v>787095584</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1231,13 +1227,13 @@
       <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="3">
         <v>781990323</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="33"/>
-      <c r="B7" s="36" t="s">
+      <c r="A7" s="28"/>
+      <c r="B7" s="31" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1247,15 +1243,15 @@
         <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F7" s="22">
+        <v>126</v>
+      </c>
+      <c r="F7" s="3">
         <v>710019414</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="33"/>
-      <c r="B8" s="36" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="31" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1267,13 +1263,13 @@
       <c r="E8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="2">
         <v>786241255</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="34"/>
-      <c r="B9" s="37" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="32" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1285,15 +1281,15 @@
       <c r="E9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="3">
         <v>789160171</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="30" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1305,13 +1301,13 @@
       <c r="E10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="2">
         <v>789166714</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="33"/>
-      <c r="B11" s="36" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="31" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1323,13 +1319,13 @@
       <c r="E11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="33"/>
-      <c r="B12" s="36" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="31" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1341,567 +1337,567 @@
       <c r="E12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="2">
         <v>789166702</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="34"/>
-      <c r="B13" s="37" t="s">
+      <c r="A13" s="29"/>
+      <c r="B13" s="32" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="2">
+        <v>711630278</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="B14" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="21">
-        <v>787655205</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="32" t="s">
+      <c r="D14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="E14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="33"/>
-      <c r="B15" s="36" t="s">
-        <v>46</v>
+      <c r="A15" s="28"/>
+      <c r="B15" s="31" t="s">
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="21">
+        <v>49</v>
+      </c>
+      <c r="F15" s="2">
         <v>787080726</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="33"/>
-      <c r="B16" s="36" t="s">
-        <v>46</v>
+      <c r="A16" s="28"/>
+      <c r="B16" s="31" t="s">
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2">
+        <v>787081068</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="29"/>
+      <c r="B17" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="21">
-        <v>787081068</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="34"/>
-      <c r="B17" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2">
+        <v>781590999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="B18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="21">
-        <v>781590999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="32" t="s">
+      <c r="D18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="F18" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="28"/>
+      <c r="B19" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="33"/>
-      <c r="B19" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="28"/>
+      <c r="B20" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="E20" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="33"/>
-      <c r="B20" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="2" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="29"/>
+      <c r="B21" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="E21" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="34"/>
-      <c r="B21" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="7">
+        <v>789167632</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="B22" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F21" s="24">
-        <v>789167632</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="32" t="s">
+      <c r="D22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="E22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2">
+        <v>775810336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="B23" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="21">
-        <v>775810336</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="33" t="s">
+      <c r="E23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2">
+        <v>778525987</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="21">
-        <v>778525987</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" s="2">
+        <v>772104981</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="21">
-        <v>772104981</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="E25" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F25" s="11">
         <v>789168927</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2">
+        <v>777410048</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="21">
-        <v>777410048</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>83</v>
+      <c r="B27" s="31" t="s">
+        <v>80</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F27" s="12">
         <v>787084130</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="F28" s="2">
+        <v>776019823</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="21">
-        <v>776019823</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="F29" s="2">
+        <v>782981141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="30" t="s">
         <v>91</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" s="21">
-        <v>782981141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="35" t="s">
-        <v>94</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F30" s="25">
+        <v>155</v>
+      </c>
+      <c r="F30">
         <v>710021900</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="36" t="s">
+      <c r="A31" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31" s="3">
+        <v>789157751</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F32" s="3">
+        <v>789166902</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="F33" s="2">
+        <v>789166982</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.4">
+      <c r="A34" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F31" s="22">
-        <v>789157751</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F32" s="22">
-        <v>789166902</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="18" t="s">
+      <c r="C34" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E33" s="17" t="s">
+      <c r="D34" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="19" t="s">
         <v>157</v>
-      </c>
-      <c r="F33" s="21">
-        <v>789166982</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A34" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>160</v>
       </c>
       <c r="F34" s="11">
         <v>710017946</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="33"/>
-      <c r="B35" s="36" t="s">
+      <c r="A35" s="28"/>
+      <c r="B35" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="F35" s="2">
+        <v>781180552</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="28"/>
+      <c r="B36" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F35" s="21">
-        <v>781180552</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="33"/>
-      <c r="B36" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="F36" s="2">
+        <v>787080588</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="29"/>
+      <c r="B37" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D37" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="F37" s="2">
+        <v>789150406</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="F36" s="21">
-        <v>787080588</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="34"/>
-      <c r="B37" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="21">
-        <v>789150406</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" s="2">
+        <v>771545210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F38" s="21">
-        <v>771545210</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="F39" s="2">
+        <v>773958904</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F39" s="21">
-        <v>773958904</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="F40" s="2">
+        <v>776950987</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="21">
-        <v>776950987</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" s="21">
+      <c r="F41" s="2">
         <v>781825193</v>
       </c>
     </row>
@@ -1909,141 +1905,141 @@
       <c r="A42" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="35" t="s">
-        <v>118</v>
+      <c r="B42" s="30" t="s">
+        <v>115</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F42" s="21">
+        <v>116</v>
+      </c>
+      <c r="F42" s="2">
         <v>786180521</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
-      <c r="B43" s="36" t="s">
-        <v>118</v>
+      <c r="B43" s="31" t="s">
+        <v>115</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="21">
+        <v>117</v>
+      </c>
+      <c r="F43" s="2">
         <v>786183517</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
-      <c r="B44" s="36" t="s">
+      <c r="B44" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F44" s="21">
+      <c r="F44" s="2">
         <v>772118585</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
-      <c r="B45" s="36" t="s">
-        <v>118</v>
+      <c r="B45" s="31" t="s">
+        <v>115</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E45" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F45" s="8">
+        <v>789157530</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="F45" s="26">
-        <v>789157530</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>141</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>27</v>
       </c>
       <c r="E46" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" s="22">
+        <v>789217447</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="25"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F46" s="27">
-        <v>789217447</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F47" s="27">
+      <c r="F47" s="22">
         <v>783059147</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31"/>
+      <c r="A48" s="25"/>
+      <c r="B48" s="26"/>
       <c r="C48" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F48" s="23">
+        <v>787979910</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="25"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D49" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E49" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F48" s="28">
-        <v>787979910</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="F49" s="28">
+      <c r="F49" s="23">
         <v>789514893</v>
       </c>
     </row>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonatelworkplace-my.sharepoint.com/personal/fall7435_orange-sonatel_com/Documents/Bureau/DOSSIER LOUMAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{40ED9D43-4F44-4B93-A6D3-4D729016E810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D922CF88-E92E-4202-957E-3798E5CC74D3}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{40ED9D43-4F44-4B93-A6D3-4D729016E810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6A2167D-153D-4D25-80AC-49A4E6959D50}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="162">
   <si>
     <t>DRV</t>
   </si>
@@ -477,12 +477,6 @@
     <t>Pvt_tdc590021</t>
   </si>
   <si>
-    <t>ASSANE</t>
-  </si>
-  <si>
-    <t>pvt_tbogo1864</t>
-  </si>
-  <si>
     <t>GNIMA</t>
   </si>
   <si>
@@ -556,6 +550,15 @@
   </si>
   <si>
     <t>pvt_dfallf0510</t>
+  </si>
+  <si>
+    <t>IBRAHIMA</t>
+  </si>
+  <si>
+    <t>SOUGOU</t>
+  </si>
+  <si>
+    <t>pvt_tbogo1398</t>
   </si>
 </sst>
 </file>
@@ -767,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -782,7 +785,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -805,11 +807,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -820,15 +822,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1139,15 +1143,15 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="19" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="24" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1164,8 +1168,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="28"/>
-      <c r="B3" s="31"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1180,8 +1184,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="28"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="25"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1196,8 +1200,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="29"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1212,10 +1216,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1232,8 +1236,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="28"/>
-      <c r="B7" s="31" t="s">
+      <c r="A7" s="27"/>
+      <c r="B7" s="25" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1250,8 +1254,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="28"/>
-      <c r="B8" s="31" t="s">
+      <c r="A8" s="27"/>
+      <c r="B8" s="25" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1268,8 +1272,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="29"/>
-      <c r="B9" s="32" t="s">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1286,10 +1290,10 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="24" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1306,8 +1310,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="28"/>
-      <c r="B11" s="31" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="25" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1319,13 +1323,13 @@
       <c r="E11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="20" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="28"/>
-      <c r="B12" s="31" t="s">
+      <c r="A12" s="27"/>
+      <c r="B12" s="25" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1342,28 +1346,28 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="29"/>
-      <c r="B13" s="32" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F13" s="2">
         <v>711630278</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="24" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1375,13 +1379,13 @@
       <c r="E14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="20" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="28"/>
-      <c r="B15" s="31" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="25" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1398,12 +1402,12 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="28"/>
-      <c r="B16" s="31" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="25" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>27</v>
@@ -1416,8 +1420,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="29"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1434,10 +1438,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="24" t="s">
         <v>55</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1449,13 +1453,13 @@
       <c r="E18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="20" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="28"/>
-      <c r="B19" s="31" t="s">
+      <c r="A19" s="27"/>
+      <c r="B19" s="25" t="s">
         <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1467,13 +1471,13 @@
       <c r="E19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="28"/>
-      <c r="B20" s="31" t="s">
+      <c r="A20" s="27"/>
+      <c r="B20" s="25" t="s">
         <v>55</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1485,13 +1489,13 @@
       <c r="E20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="20" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="29"/>
-      <c r="B21" s="32" t="s">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1508,10 +1512,10 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="24" t="s">
         <v>70</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1528,10 +1532,10 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="25" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1548,10 +1552,10 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="25" t="s">
         <v>70</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1568,30 +1572,30 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="29" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="F25" s="11">
+      <c r="E25" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="10">
         <v>789168927</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="24" t="s">
         <v>80</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1608,30 +1612,30 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="F27" s="12">
+      <c r="F27" s="11">
         <v>787084130</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="25" t="s">
         <v>80</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -1648,10 +1652,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="29" t="s">
         <v>80</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -1668,30 +1672,30 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="13" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>155</v>
+      <c r="E30" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="F30">
         <v>710021900</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="25" t="s">
         <v>91</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -1708,10 +1712,10 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="25" t="s">
         <v>91</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -1728,48 +1732,48 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="D33" s="15" t="s">
+      <c r="C33" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E33" s="17" t="s">
-        <v>154</v>
+      <c r="E33" s="16" t="s">
+        <v>152</v>
       </c>
       <c r="F33" s="2">
         <v>789166982</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C34" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="D34" s="16" t="s">
+      <c r="C34" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="F34" s="11">
+      <c r="E34" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F34" s="10">
         <v>710017946</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="28"/>
-      <c r="B35" s="31" t="s">
+      <c r="A35" s="27"/>
+      <c r="B35" s="25" t="s">
         <v>94</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -1786,8 +1790,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="28"/>
-      <c r="B36" s="31" t="s">
+      <c r="A36" s="27"/>
+      <c r="B36" s="25" t="s">
         <v>94</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -1804,15 +1808,15 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="29"/>
-      <c r="B37" s="32" t="s">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29" t="s">
         <v>94</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>102</v>
@@ -1822,10 +1826,10 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="24" t="s">
         <v>103</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -1842,10 +1846,10 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="28" t="s">
+      <c r="A39" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -1862,10 +1866,10 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -1882,10 +1886,10 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="29" t="s">
         <v>103</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -1905,14 +1909,14 @@
       <c r="A42" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="24" t="s">
         <v>115</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>116</v>
@@ -1923,14 +1927,14 @@
     </row>
     <row r="43" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="25" t="s">
         <v>115</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>117</v>
@@ -1941,14 +1945,14 @@
     </row>
     <row r="44" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="25" t="s">
         <v>115</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>118</v>
@@ -1959,61 +1963,61 @@
     </row>
     <row r="45" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="F45" s="8">
-        <v>789157530</v>
+      <c r="C45" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="33">
+        <v>786182137</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="26" t="s">
+      <c r="B46" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="21">
+        <v>789217447</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="9" t="s">
+      <c r="D47" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F46" s="22">
-        <v>789217447</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="25"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="9" t="s">
+      <c r="E47" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D47" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F47" s="22">
+      <c r="F47" s="21">
         <v>783059147</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="25"/>
-      <c r="B48" s="26"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="31"/>
       <c r="C48" s="6" t="s">
         <v>120</v>
       </c>
@@ -2023,13 +2027,13 @@
       <c r="E48" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F48" s="23">
+      <c r="F48" s="22">
         <v>787979910</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="25"/>
-      <c r="B49" s="26"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="31"/>
       <c r="C49" s="6" t="s">
         <v>123</v>
       </c>
@@ -2039,20 +2043,13 @@
       <c r="E49" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F49" s="23">
+      <c r="F49" s="22">
         <v>789514893</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="23">
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="A2:A5"/>
@@ -2069,6 +2066,13 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/vto_list.xlsx
+++ b/vto_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonatelworkplace-my.sharepoint.com/personal/fall7435_orange-sonatel_com/Documents/Bureau/DOSSIER LOUMAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{40ED9D43-4F44-4B93-A6D3-4D729016E810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6A2167D-153D-4D25-80AC-49A4E6959D50}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{40ED9D43-4F44-4B93-A6D3-4D729016E810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5013ACF0-A257-4651-BF2A-3389E7E82604}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="160">
   <si>
     <t>DRV</t>
   </si>
@@ -261,18 +261,6 @@
     <t> 775801980</t>
   </si>
   <si>
-    <t>KHADIDIATOU</t>
-  </si>
-  <si>
-    <t>SOUARE</t>
-  </si>
-  <si>
-    <t>pvt_sosy165</t>
-  </si>
-  <si>
-    <t> 781596632</t>
-  </si>
-  <si>
     <t>MAHAMADOU</t>
   </si>
   <si>
@@ -559,13 +547,19 @@
   </si>
   <si>
     <t>pvt_tbogo1398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AISSATA </t>
+  </si>
+  <si>
+    <t>pvt_sosy0691</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -643,6 +637,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -770,7 +776,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -807,11 +813,12 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -822,17 +829,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1148,10 +1155,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1168,8 +1175,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="27"/>
-      <c r="B3" s="25"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1184,8 +1191,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="27"/>
-      <c r="B4" s="25"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1200,8 +1207,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1216,10 +1223,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1236,8 +1243,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="27"/>
-      <c r="B7" s="25" t="s">
+      <c r="A7" s="28"/>
+      <c r="B7" s="31" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1247,15 +1254,15 @@
         <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F7" s="3">
         <v>710019414</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="27"/>
-      <c r="B8" s="25" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="31" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1272,8 +1279,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="32" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1290,10 +1297,10 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="30" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1310,8 +1317,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="27"/>
-      <c r="B11" s="25" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="31" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1328,8 +1335,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="27"/>
-      <c r="B12" s="25" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="31" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1346,28 +1353,28 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29" t="s">
+      <c r="A13" s="29"/>
+      <c r="B13" s="32" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F13" s="2">
         <v>711630278</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="30" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1384,8 +1391,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="27"/>
-      <c r="B15" s="25" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="31" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1402,12 +1409,12 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="27"/>
-      <c r="B16" s="25" t="s">
+      <c r="A16" s="28"/>
+      <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>27</v>
@@ -1420,8 +1427,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1438,10 +1445,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="30" t="s">
         <v>55</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1458,8 +1465,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="27"/>
-      <c r="B19" s="25" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="31" t="s">
         <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1476,430 +1483,430 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="27"/>
-      <c r="B20" s="25" t="s">
+      <c r="A20" s="28"/>
+      <c r="B20" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="34">
+        <v>710016420</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="29"/>
+      <c r="B21" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="F21" s="7">
         <v>789167632</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="F22" s="2">
         <v>775810336</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="25" t="s">
+      <c r="A23" s="28" t="s">
         <v>70</v>
       </c>
+      <c r="B23" s="31" t="s">
+        <v>66</v>
+      </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F23" s="2">
         <v>778525987</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="F24" s="2">
         <v>772104981</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E25" s="10" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F25" s="10">
         <v>789168927</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="24" t="s">
-        <v>80</v>
+      <c r="B26" s="30" t="s">
+        <v>76</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F26" s="2">
         <v>777410048</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="25" t="s">
+      <c r="A27" s="28" t="s">
         <v>80</v>
       </c>
+      <c r="B27" s="31" t="s">
+        <v>76</v>
+      </c>
       <c r="C27" s="11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F27" s="11">
         <v>787084130</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="25" t="s">
+      <c r="A28" s="28" t="s">
         <v>80</v>
       </c>
+      <c r="B28" s="31" t="s">
+        <v>76</v>
+      </c>
       <c r="C28" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F28" s="2">
         <v>776019823</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F29" s="2">
         <v>782981141</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="24" t="s">
-        <v>91</v>
+      <c r="B30" s="30" t="s">
+        <v>87</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F30">
         <v>710021900</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>91</v>
+      <c r="A31" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>87</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F31" s="3">
         <v>789157751</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>91</v>
+      <c r="A32" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>87</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F32" s="3">
         <v>789166902</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>91</v>
+      <c r="A33" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>87</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F33" s="2">
         <v>789166982</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="24" t="s">
-        <v>94</v>
+      <c r="B34" s="30" t="s">
+        <v>90</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F34" s="10">
         <v>710017946</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="27"/>
-      <c r="B35" s="25" t="s">
-        <v>94</v>
+      <c r="A35" s="28"/>
+      <c r="B35" s="31" t="s">
+        <v>90</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F35" s="2">
         <v>781180552</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="27"/>
-      <c r="B36" s="25" t="s">
+      <c r="A36" s="28"/>
+      <c r="B36" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F36" s="2">
         <v>787080588</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="28"/>
-      <c r="B37" s="29" t="s">
-        <v>94</v>
+      <c r="A37" s="29"/>
+      <c r="B37" s="32" t="s">
+        <v>90</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F37" s="2">
         <v>789150406</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="24" t="s">
-        <v>103</v>
+      <c r="A38" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>99</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F38" s="2">
         <v>771545210</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" s="25" t="s">
+      <c r="A39" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E39" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F39" s="2">
         <v>773958904</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>103</v>
+      <c r="A40" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>99</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F40" s="2">
         <v>776950987</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B41" s="29" t="s">
-        <v>103</v>
+      <c r="A41" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>99</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F41" s="2">
         <v>781825193</v>
@@ -1909,17 +1916,17 @@
       <c r="A42" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="24" t="s">
-        <v>115</v>
+      <c r="B42" s="30" t="s">
+        <v>111</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F42" s="2">
         <v>786180521</v>
@@ -1927,17 +1934,17 @@
     </row>
     <row r="43" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
-      <c r="B43" s="25" t="s">
-        <v>115</v>
+      <c r="B43" s="31" t="s">
+        <v>111</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F43" s="2">
         <v>786183517</v>
@@ -1945,17 +1952,17 @@
     </row>
     <row r="44" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
-      <c r="B44" s="25" t="s">
-        <v>115</v>
+      <c r="B44" s="31" t="s">
+        <v>111</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F44" s="2">
         <v>772118585</v>
@@ -1963,85 +1970,85 @@
     </row>
     <row r="45" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
-      <c r="B45" s="25" t="s">
+      <c r="B45" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E45" t="s">
+        <v>157</v>
+      </c>
+      <c r="F45">
+        <v>786182137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="D45" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E45" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="F45" s="33">
-        <v>786182137</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="31" t="s">
-        <v>119</v>
-      </c>
       <c r="C46" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F46" s="21">
         <v>789217447</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
+      <c r="A47" s="25"/>
+      <c r="B47" s="26"/>
       <c r="C47" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F47" s="21">
         <v>783059147</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31"/>
+      <c r="A48" s="25"/>
+      <c r="B48" s="26"/>
       <c r="C48" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F48" s="22">
         <v>787979910</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
+      <c r="A49" s="25"/>
+      <c r="B49" s="26"/>
       <c r="C49" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F49" s="22">
         <v>789514893</v>
@@ -2050,6 +2057,13 @@
   </sheetData>
   <autoFilter ref="A1:F45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="23">
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="A2:A5"/>
@@ -2066,13 +2080,6 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
